--- a/src/DefineFromExcel/DDS_excel/Templates/Template1/Sample1_schema_validation.xlsx
+++ b/src/DefineFromExcel/DDS_excel/Templates/Template1/Sample1_schema_validation.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>type='jsonschema validation' severity=&lt;Severity.ERROR: 'ERROR'&gt; message="{'OID': 'IG.SC', 'name': 'SC', 'description': 'Subject Characteristics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SC.STUDYID', 'IT.SC.DOMAIN', 'IT.SC.USUBJID', 'IT.SC.SCSEQ', 'IT.SC.SCTESTCD', 'IT.SC.SCTEST', 'IT.SC.SCCAT', 'IT.SC.SCORRES', 'IT.SC.SCORRESU', 'IT.SC.SCSTRESC', 'IT.SC.SCSTRESN', 'IT.SC.SCSTRESU', 'IT.SC.SCDTC', 'IT.SC.SCDY'], 'keySequence': ['IT.SC.STUDYID', 'IT.SC.USUBJID']} is not valid under any of the given schemas in /itemGroups/0" instance={'OID': 'MDV.360i CDISC PILOT - LZZT', 'name': 'MDV 360i CDISC PILOT - LZZT', 'description': 'Data Definitions for 360i CDISC PILOT - LZZT', 'fileOID': 'ODM.DEFINE-360I.360i CDISC PILOT - LZZT', 'creationDateTime': '2026-04-15T20:36:55.421402+00:00', 'odmVersion': '1.3.2', 'fileType': 'Snapshot', 'originator': 'Define-360i Processor', 'context': 'Other', 'defineVersion': '2.1.0', 'studyOID': '', 'studyName': '360i CDISC PILOT - LZZT', 'studyDescription': "Safety and Efficacy of the Xanomeline Transdermal Therapeutic System (TTS) in Patients with Mild to Moderate Alzheimer's Disease", 'protocolName': '360i LZZT Xanomeline (LY246708)', 'itemGroups': [{'OID': 'IG.SC', 'name': 'SC', 'description': 'Subject Characteristics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SC.STUDYID', 'IT.SC.DOMAIN', 'IT.SC.USUBJID', 'IT.SC.SCSEQ', 'IT.SC.SCTESTCD', 'IT.SC.SCTEST', 'IT.SC.SCCAT', 'IT.SC.SCORRES', 'IT.SC.SCORRESU', 'IT.SC.SCSTRESC', 'IT.SC.SCSTRESN', 'IT.SC.SCSTRESU', 'IT.SC.SCDTC', 'IT.SC.SCDY'], 'keySequence': ['IT.SC.STUDYID', 'IT.SC.USUBJID']}, {'OID': 'IG.LB', 'name': 'LB', 'description': 'Laboratory Test Findings', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.LB.STUDYID', 'IT.LB.DOMAIN', 'IT.LB.USUBJID', 'IT.LB.LBSEQ', 'IT.LB.LBTESTCD', 'IT.LB.LBTEST', 'IT.LB.LBCAT', 'IT.LB.LBORRES', 'IT.LB.LBORRESU', 'IT.LB.LBORNRLO', 'IT.LB.LBORNRHI', 'IT.LB.LBSTRESC', 'IT.LB.LBSTRESN', 'IT.LB.LBSTRESU', 'IT.LB.LBSTNRLO', 'IT.LB.LBSTNRHI', 'IT.LB.LBNRIND', 'IT.LB.LBBLFL', 'IT.LB.VISITNUM', 'IT.LB.VISIT', 'IT.LB.VISITDY', 'IT.LB.LBDTC', 'IT.LB.LBDY'], 'keySequence': ['IT.LB.STUDYID', 'IT.LB.USUBJID']}, {'OID': 'IG.AE', 'name': 'AE', 'description': 'Adverse Events', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.AE.STUDYID', 'IT.AE.DOMAIN', 'IT.AE.USUBJID', 'IT.AE.AESEQ', 'IT.AE.AESPID', 'IT.AE.AETERM', 'IT.AE.AELLT', 'IT.AE.AELLTCD', 'IT.AE.AEDECOD', 'IT.AE.AEPTCD', 'IT.AE.AEHLT', 'IT.AE.AEHLTCD', 'IT.AE.AEHLGT', 'IT.AE.AEHLGTCD', 'IT.AE.AEBODSYS', 'IT.AE.AEBDSYCD', 'IT.AE.AESOC', 'IT.AE.AESOCCD', 'IT.AE.AESEV', 'IT.AE.AESER', 'IT.AE.AEACN', 'IT.AE.AEREL', 'IT.AE.AEOUT', 'IT.AE.AESCAN', 'IT.AE.AESCONG', 'IT.AE.AESDISAB', 'IT.AE.AESDTH', 'IT.AE.AESHOSP', 'IT.AE.AESLIFE', 'IT.AE.AESOD', 'IT.AE.AEDTC', 'IT.AE.AESTDTC', 'IT.AE.AEENDTC', 'IT.AE.AESTDY', 'IT.AE.AEENDY'], 'keySequence': ['IT.AE.STUDYID', 'IT.AE.USUBJID']}, {'OID': 'IG.QS', 'name': 'QS', 'description': 'Questionnaires', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.QS.STUDYID', 'IT.QS.DOMAIN', 'IT.QS.USUBJID', 'IT.QS.QSSEQ', 'IT.QS.QSTESTCD', 'IT.QS.QSTEST', 'IT.QS.QSCAT', 'IT.QS.QSSCAT', 'IT.QS.QSORRES', 'IT.QS.QSORRESU', 'IT.QS.QSSTRESC', 'IT.QS.QSSTRESN', 'IT.QS.QSSTRESU', 'IT.QS.QSBLFL', 'IT.QS.QSDRVFL', 'IT.QS.VISITNUM', 'IT.QS.VISIT', 'IT.QS.VISITDY', 'IT.QS.QSDTC', 'IT.QS.QSDY'], 'keySequence': ['IT.QS.STUDYID', 'IT.QS.USUBJID']}, {'OID': 'IG.DM', 'name': 'DM', 'description': 'Demographics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DM.STUDYID', 'IT.DM.SITEID', 'IT.DM.DOMAIN', 'IT.DM.USUBJID', 'IT.DM.SUBJID', 'IT.DM.RFSTDTC', 'IT.DM.RFENDTC', 'IT.DM.RFXSTDTC', 'IT.DM.RFXENDTC', 'IT.DM.RFICDTC', 'IT.DM.RFPENDTC', 'IT.DM.DTHDTC', 'IT.DM.DTHFL', 'IT.DM.AGE', 'IT.DM.AGEU', 'IT.DM.SEX', 'IT.DM.RACE', 'IT.DM.ETHNIC', 'IT.DM.COUNTRY', 'IT.DM.ARM', 'IT.DM.ARMCD', 'IT.DM.ACTARM', 'IT.DM.ACTARMCD', 'IT.DM.DMDTC', 'IT.DM.DMDY'], 'keySequence': ['IT.DM.STUDYID', 'IT.DM.USUBJID']}, {'OID': 'IG.CM', 'name': 'CM', 'description': 'Concomitant Medications', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.CM.STUDYID', 'IT.CM.DOMAIN', 'IT.CM.USUBJID', 'IT.CM.CMSEQ', 'IT.CM.CMSPID', 'IT.CM.CMTRT', 'IT.CM.CMDECOD', 'IT.CM.CMINDC', 'IT.CM.CMCLAS', 'IT.CM.CMDOSE', 'IT.CM.CMDOSU', 'IT.CM.CMDOSFRQ', 'IT.CM.CMROUTE', 'IT.CM.VISITNUM', 'IT.CM.VISIT', 'IT.CM.VISITDY', 'IT.CM.CMDTC', 'IT.CM.CMSTDTC', 'IT.CM.CMENDTC', 'IT.CM.CMSTDY', 'IT.CM.CMENDY'], 'keySequence': ['IT.CM.STUDYID', 'IT.CM.USUBJID']}, {'OID': 'IG.SUPPDS', 'name': 'SUPPDS', 'description': 'Supplemental Qualifiers for DS', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.RDOMAIN', 'IT.SUPPDS.USUBJID', 'IT.SUPPDS.IDVAR', 'IT.SUPPDS.IDVARVAL', 'IT.SUPPDS.QNAM', 'IT.SUPPDS.QLABEL', 'IT.SUPPDS.QVAL', 'IT.SUPPDS.QORIG', 'IT.SUPPDS.QEVAL'], 'keySequence': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.USUBJID']}, {'OID': 'IG.EX', 'name': 'EX', 'description': 'Exposure', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.EX.STUDYID', 'IT.EX.DOMAIN', 'IT.EX.USUBJID', 'IT.EX.EXSEQ', 'IT.EX.EXTRT', 'IT.EX.EXDOSE', 'IT.EX.EXDOSU', 'IT.EX.EXDOSFRM', 'IT.EX.EXDOSFRQ', 'IT.EX.EXROUTE', 'IT.EX.VISITNUM', 'IT.EX.VISIT', 'IT.EX.VISITDY', 'IT.EX.EXSTDTC', 'IT.EX.EXENDTC', 'IT.EX.EXSTDY', 'IT.EX.EXENDY'], 'keySequence': ['IT.EX.STUDYID', 'IT.EX.USUBJID']}, {'OID': 'IG.VS', 'name': 'VS', 'description': 'Vital Signs', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.VS.STUDYID', 'IT.VS.DOMAIN', 'IT.VS.USUBJID', 'IT.VS.VSSEQ', 'IT.VS.VSTESTCD', 'IT.VS.VSTEST', 'IT.VS.VSPOS', 'IT.VS.VSORRES', 'IT.VS.VSORRESU', 'IT.VS.VSSTRESC', 'IT.VS.VSSTRESN', 'IT.VS.VSSTRESU', 'IT.VS.VSSTAT', 'IT.VS.VSLOC', 'IT.VS.VSBLFL', 'IT.VS.VISITNUM', 'IT.VS.VISIT', 'IT.VS.VISITDY', 'IT.VS.VSDTC', 'IT.VS.VSDY', 'IT.VS.VSTPT', 'IT.VS.VSTPTNUM', 'IT.VS.VSELTM', 'IT.VS.VSTPTREF'], 'keySequence': ['IT.VS.STUDYID', 'IT.VS.USUBJID']}, {'OID': 'IG.MH', 'name': 'MH', 'description': 'Medical History', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.MH.STUDYID', 'IT.MH.DOMAIN', 'IT.MH.USUBJID', 'IT.MH.MHSEQ', 'IT.MH.MHSPID', 'IT.MH.MHTERM', 'IT.MH.MHLLT', 'IT.MH.MHDECOD', 'IT.MH.MHHLT', 'IT.MH.MHHLGT', 'IT.MH.MHCAT', 'IT.MH.MHBODSYS', 'IT.MH.MHSEV', 'IT.MH.VISITNUM', 'IT.MH.VISIT', 'IT.MH.VISITDY', 'IT.MH.MHDTC', 'IT.MH.MHSTDTC', 'IT.MH.MHDY'], 'keySequence': ['IT.MH.STUDYID', 'IT.MH.USUBJID']}, {'OID': 'IG.DS', 'name': 'DS', 'description': 'Disposition', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DS.STUDYID', 'IT.DS.DOMAIN', 'IT.DS.USUBJID', 'IT.DS.DSSEQ', 'IT.DS.DSSPID', 'IT.DS.DSTERM', 'IT.DS.DSDECOD', 'IT.DS.DSCAT', 'IT.DS.VISITNUM', 'IT.DS.VISIT', 'IT.DS.DSDTC', 'IT.DS.DSSTDTC', 'IT.DS.DSSTDY'], 'keySequence': ['IT.DS.STUDYID', 'IT.DS.USUBJID']}], 'standards': [{'OID': 'STD.1', 'name': 'SDTMIG', 'type': 'IG', 'version': '3.4', 'status': 'Final'}, {'OID': 'STD.2', 'name': 'CDISC/NCI', 'type': 'CT', 'version': '2024-09-27', 'status': 'Final'}]} instance_index=0 instantiates='MetaDataVersion' context=["'IT.SC.STUDYID' is not of type 'object'", "'IT.SC.DOMAIN' is not of type 'object'", "'IT.SC.USUBJID' is not of type 'object'", "'IT.SC.SCSEQ' is not of type 'object'", "'IT.SC.SCTESTCD' is not of type 'object'", "'IT.SC.SCTEST' is not of type 'object'", "'IT.SC.SCCAT' is not of type 'object'", "'IT.SC.SCORRES' is not of type 'object'", "'IT.SC.SCORRESU' is not of type 'object'", "'IT.SC.SCSTRESC' is not of type 'object'", "'IT.SC.SCSTRESN' is not of type 'object'", "'IT.SC.SCSTRESU' is not of type 'object'", "'IT.SC.SCDTC' is not of type 'object'", "'IT.SC.SCDY' is not of type 'object'", "'IT.SC.STUDYID' is not of type 'object'", "'IT.SC.USUBJID' is not of type 'object'", "'IT.SC.STUDYID' is not of type 'object'", "'IT.SC.DOMAIN' is not of type 'object'", "'IT.SC.USUBJID' is not of type 'object'", "'IT.SC.SCSEQ' is not of type 'object'", "'IT.SC.SCTESTCD' is not of type 'object'", "'IT.SC.SCTEST' is not of type 'object'", "'IT.SC.SCCAT' is not of type 'object'", "'IT.SC.SCORRES' is not of type 'object'", "'IT.SC.SCORRESU' is not of type 'object'", "'IT.SC.SCSTRESC' is not of type 'object'", "'IT.SC.SCSTRESN' is not of type 'object'", "'IT.SC.SCSTRESU' is not of type 'object'", "'IT.SC.SCDTC' is not of type 'object'", "'IT.SC.SCDY' is not of type 'object'", "'IT.SC.STUDYID' is not of type 'object'", "'IT.SC.USUBJID' is not of type 'object'"] source=&lt;ValidationError: "{'OID': 'IG.SC', 'name': 'SC', 'description': 'Subject Characteristics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SC.STUDYID', 'IT.SC.DOMAIN', 'IT.SC.USUBJID', 'IT.SC.SCSEQ', 'IT.SC.SCTESTCD', 'IT.SC.SCTEST', 'IT.SC.SCCAT', 'IT.SC.SCORRES', 'IT.SC.SCORRESU', 'IT.SC.SCSTRESC', 'IT.SC.SCSTRESN', 'IT.SC.SCSTRESU', 'IT.SC.SCDTC', 'IT.SC.SCDY'], 'keySequence': ['IT.SC.STUDYID', 'IT.SC.USUBJID']} is not valid under any of the given schemas"&gt;</t>
+          <t>'OID' is a required property in /items/107/origin/documents/0</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>type='jsonschema validation' severity=&lt;Severity.ERROR: 'ERROR'&gt; message="{'OID': 'IG.LB', 'name': 'LB', 'description': 'Laboratory Test Findings', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.LB.STUDYID', 'IT.LB.DOMAIN', 'IT.LB.USUBJID', 'IT.LB.LBSEQ', 'IT.LB.LBTESTCD', 'IT.LB.LBTEST', 'IT.LB.LBCAT', 'IT.LB.LBORRES', 'IT.LB.LBORRESU', 'IT.LB.LBORNRLO', 'IT.LB.LBORNRHI', 'IT.LB.LBSTRESC', 'IT.LB.LBSTRESN', 'IT.LB.LBSTRESU', 'IT.LB.LBSTNRLO', 'IT.LB.LBSTNRHI', 'IT.LB.LBNRIND', 'IT.LB.LBBLFL', 'IT.LB.VISITNUM', 'IT.LB.VISIT', 'IT.LB.VISITDY', 'IT.LB.LBDTC', 'IT.LB.LBDY'], 'keySequence': ['IT.LB.STUDYID', 'IT.LB.USUBJID']} is not valid under any of the given schemas in /itemGroups/1" instance={'OID': 'MDV.360i CDISC PILOT - LZZT', 'name': 'MDV 360i CDISC PILOT - LZZT', 'description': 'Data Definitions for 360i CDISC PILOT - LZZT', 'fileOID': 'ODM.DEFINE-360I.360i CDISC PILOT - LZZT', 'creationDateTime': '2026-04-15T20:36:55.421402+00:00', 'odmVersion': '1.3.2', 'fileType': 'Snapshot', 'originator': 'Define-360i Processor', 'context': 'Other', 'defineVersion': '2.1.0', 'studyOID': '', 'studyName': '360i CDISC PILOT - LZZT', 'studyDescription': "Safety and Efficacy of the Xanomeline Transdermal Therapeutic System (TTS) in Patients with Mild to Moderate Alzheimer's Disease", 'protocolName': '360i LZZT Xanomeline (LY246708)', 'itemGroups': [{'OID': 'IG.SC', 'name': 'SC', 'description': 'Subject Characteristics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SC.STUDYID', 'IT.SC.DOMAIN', 'IT.SC.USUBJID', 'IT.SC.SCSEQ', 'IT.SC.SCTESTCD', 'IT.SC.SCTEST', 'IT.SC.SCCAT', 'IT.SC.SCORRES', 'IT.SC.SCORRESU', 'IT.SC.SCSTRESC', 'IT.SC.SCSTRESN', 'IT.SC.SCSTRESU', 'IT.SC.SCDTC', 'IT.SC.SCDY'], 'keySequence': ['IT.SC.STUDYID', 'IT.SC.USUBJID']}, {'OID': 'IG.LB', 'name': 'LB', 'description': 'Laboratory Test Findings', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.LB.STUDYID', 'IT.LB.DOMAIN', 'IT.LB.USUBJID', 'IT.LB.LBSEQ', 'IT.LB.LBTESTCD', 'IT.LB.LBTEST', 'IT.LB.LBCAT', 'IT.LB.LBORRES', 'IT.LB.LBORRESU', 'IT.LB.LBORNRLO', 'IT.LB.LBORNRHI', 'IT.LB.LBSTRESC', 'IT.LB.LBSTRESN', 'IT.LB.LBSTRESU', 'IT.LB.LBSTNRLO', 'IT.LB.LBSTNRHI', 'IT.LB.LBNRIND', 'IT.LB.LBBLFL', 'IT.LB.VISITNUM', 'IT.LB.VISIT', 'IT.LB.VISITDY', 'IT.LB.LBDTC', 'IT.LB.LBDY'], 'keySequence': ['IT.LB.STUDYID', 'IT.LB.USUBJID']}, {'OID': 'IG.AE', 'name': 'AE', 'description': 'Adverse Events', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.AE.STUDYID', 'IT.AE.DOMAIN', 'IT.AE.USUBJID', 'IT.AE.AESEQ', 'IT.AE.AESPID', 'IT.AE.AETERM', 'IT.AE.AELLT', 'IT.AE.AELLTCD', 'IT.AE.AEDECOD', 'IT.AE.AEPTCD', 'IT.AE.AEHLT', 'IT.AE.AEHLTCD', 'IT.AE.AEHLGT', 'IT.AE.AEHLGTCD', 'IT.AE.AEBODSYS', 'IT.AE.AEBDSYCD', 'IT.AE.AESOC', 'IT.AE.AESOCCD', 'IT.AE.AESEV', 'IT.AE.AESER', 'IT.AE.AEACN', 'IT.AE.AEREL', 'IT.AE.AEOUT', 'IT.AE.AESCAN', 'IT.AE.AESCONG', 'IT.AE.AESDISAB', 'IT.AE.AESDTH', 'IT.AE.AESHOSP', 'IT.AE.AESLIFE', 'IT.AE.AESOD', 'IT.AE.AEDTC', 'IT.AE.AESTDTC', 'IT.AE.AEENDTC', 'IT.AE.AESTDY', 'IT.AE.AEENDY'], 'keySequence': ['IT.AE.STUDYID', 'IT.AE.USUBJID']}, {'OID': 'IG.QS', 'name': 'QS', 'description': 'Questionnaires', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.QS.STUDYID', 'IT.QS.DOMAIN', 'IT.QS.USUBJID', 'IT.QS.QSSEQ', 'IT.QS.QSTESTCD', 'IT.QS.QSTEST', 'IT.QS.QSCAT', 'IT.QS.QSSCAT', 'IT.QS.QSORRES', 'IT.QS.QSORRESU', 'IT.QS.QSSTRESC', 'IT.QS.QSSTRESN', 'IT.QS.QSSTRESU', 'IT.QS.QSBLFL', 'IT.QS.QSDRVFL', 'IT.QS.VISITNUM', 'IT.QS.VISIT', 'IT.QS.VISITDY', 'IT.QS.QSDTC', 'IT.QS.QSDY'], 'keySequence': ['IT.QS.STUDYID', 'IT.QS.USUBJID']}, {'OID': 'IG.DM', 'name': 'DM', 'description': 'Demographics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DM.STUDYID', 'IT.DM.SITEID', 'IT.DM.DOMAIN', 'IT.DM.USUBJID', 'IT.DM.SUBJID', 'IT.DM.RFSTDTC', 'IT.DM.RFENDTC', 'IT.DM.RFXSTDTC', 'IT.DM.RFXENDTC', 'IT.DM.RFICDTC', 'IT.DM.RFPENDTC', 'IT.DM.DTHDTC', 'IT.DM.DTHFL', 'IT.DM.AGE', 'IT.DM.AGEU', 'IT.DM.SEX', 'IT.DM.RACE', 'IT.DM.ETHNIC', 'IT.DM.COUNTRY', 'IT.DM.ARM', 'IT.DM.ARMCD', 'IT.DM.ACTARM', 'IT.DM.ACTARMCD', 'IT.DM.DMDTC', 'IT.DM.DMDY'], 'keySequence': ['IT.DM.STUDYID', 'IT.DM.USUBJID']}, {'OID': 'IG.CM', 'name': 'CM', 'description': 'Concomitant Medications', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.CM.STUDYID', 'IT.CM.DOMAIN', 'IT.CM.USUBJID', 'IT.CM.CMSEQ', 'IT.CM.CMSPID', 'IT.CM.CMTRT', 'IT.CM.CMDECOD', 'IT.CM.CMINDC', 'IT.CM.CMCLAS', 'IT.CM.CMDOSE', 'IT.CM.CMDOSU', 'IT.CM.CMDOSFRQ', 'IT.CM.CMROUTE', 'IT.CM.VISITNUM', 'IT.CM.VISIT', 'IT.CM.VISITDY', 'IT.CM.CMDTC', 'IT.CM.CMSTDTC', 'IT.CM.CMENDTC', 'IT.CM.CMSTDY', 'IT.CM.CMENDY'], 'keySequence': ['IT.CM.STUDYID', 'IT.CM.USUBJID']}, {'OID': 'IG.SUPPDS', 'name': 'SUPPDS', 'description': 'Supplemental Qualifiers for DS', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.RDOMAIN', 'IT.SUPPDS.USUBJID', 'IT.SUPPDS.IDVAR', 'IT.SUPPDS.IDVARVAL', 'IT.SUPPDS.QNAM', 'IT.SUPPDS.QLABEL', 'IT.SUPPDS.QVAL', 'IT.SUPPDS.QORIG', 'IT.SUPPDS.QEVAL'], 'keySequence': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.USUBJID']}, {'OID': 'IG.EX', 'name': 'EX', 'description': 'Exposure', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.EX.STUDYID', 'IT.EX.DOMAIN', 'IT.EX.USUBJID', 'IT.EX.EXSEQ', 'IT.EX.EXTRT', 'IT.EX.EXDOSE', 'IT.EX.EXDOSU', 'IT.EX.EXDOSFRM', 'IT.EX.EXDOSFRQ', 'IT.EX.EXROUTE', 'IT.EX.VISITNUM', 'IT.EX.VISIT', 'IT.EX.VISITDY', 'IT.EX.EXSTDTC', 'IT.EX.EXENDTC', 'IT.EX.EXSTDY', 'IT.EX.EXENDY'], 'keySequence': ['IT.EX.STUDYID', 'IT.EX.USUBJID']}, {'OID': 'IG.VS', 'name': 'VS', 'description': 'Vital Signs', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.VS.STUDYID', 'IT.VS.DOMAIN', 'IT.VS.USUBJID', 'IT.VS.VSSEQ', 'IT.VS.VSTESTCD', 'IT.VS.VSTEST', 'IT.VS.VSPOS', 'IT.VS.VSORRES', 'IT.VS.VSORRESU', 'IT.VS.VSSTRESC', 'IT.VS.VSSTRESN', 'IT.VS.VSSTRESU', 'IT.VS.VSSTAT', 'IT.VS.VSLOC', 'IT.VS.VSBLFL', 'IT.VS.VISITNUM', 'IT.VS.VISIT', 'IT.VS.VISITDY', 'IT.VS.VSDTC', 'IT.VS.VSDY', 'IT.VS.VSTPT', 'IT.VS.VSTPTNUM', 'IT.VS.VSELTM', 'IT.VS.VSTPTREF'], 'keySequence': ['IT.VS.STUDYID', 'IT.VS.USUBJID']}, {'OID': 'IG.MH', 'name': 'MH', 'description': 'Medical History', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.MH.STUDYID', 'IT.MH.DOMAIN', 'IT.MH.USUBJID', 'IT.MH.MHSEQ', 'IT.MH.MHSPID', 'IT.MH.MHTERM', 'IT.MH.MHLLT', 'IT.MH.MHDECOD', 'IT.MH.MHHLT', 'IT.MH.MHHLGT', 'IT.MH.MHCAT', 'IT.MH.MHBODSYS', 'IT.MH.MHSEV', 'IT.MH.VISITNUM', 'IT.MH.VISIT', 'IT.MH.VISITDY', 'IT.MH.MHDTC', 'IT.MH.MHSTDTC', 'IT.MH.MHDY'], 'keySequence': ['IT.MH.STUDYID', 'IT.MH.USUBJID']}, {'OID': 'IG.DS', 'name': 'DS', 'description': 'Disposition', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DS.STUDYID', 'IT.DS.DOMAIN', 'IT.DS.USUBJID', 'IT.DS.DSSEQ', 'IT.DS.DSSPID', 'IT.DS.DSTERM', 'IT.DS.DSDECOD', 'IT.DS.DSCAT', 'IT.DS.VISITNUM', 'IT.DS.VISIT', 'IT.DS.DSDTC', 'IT.DS.DSSTDTC', 'IT.DS.DSSTDY'], 'keySequence': ['IT.DS.STUDYID', 'IT.DS.USUBJID']}], 'standards': [{'OID': 'STD.1', 'name': 'SDTMIG', 'type': 'IG', 'version': '3.4', 'status': 'Final'}, {'OID': 'STD.2', 'name': 'CDISC/NCI', 'type': 'CT', 'version': '2024-09-27', 'status': 'Final'}]} instance_index=0 instantiates='MetaDataVersion' context=["'IT.LB.STUDYID' is not of type 'object'", "'IT.LB.DOMAIN' is not of type 'object'", "'IT.LB.USUBJID' is not of type 'object'", "'IT.LB.LBSEQ' is not of type 'object'", "'IT.LB.LBTESTCD' is not of type 'object'", "'IT.LB.LBTEST' is not of type 'object'", "'IT.LB.LBCAT' is not of type 'object'", "'IT.LB.LBORRES' is not of type 'object'", "'IT.LB.LBORRESU' is not of type 'object'", "'IT.LB.LBORNRLO' is not of type 'object'", "'IT.LB.LBORNRHI' is not of type 'object'", "'IT.LB.LBSTRESC' is not of type 'object'", "'IT.LB.LBSTRESN' is not of type 'object'", "'IT.LB.LBSTRESU' is not of type 'object'", "'IT.LB.LBSTNRLO' is not of type 'object'", "'IT.LB.LBSTNRHI' is not of type 'object'", "'IT.LB.LBNRIND' is not of type 'object'", "'IT.LB.LBBLFL' is not of type 'object'", "'IT.LB.VISITNUM' is not of type 'object'", "'IT.LB.VISIT' is not of type 'object'", "'IT.LB.VISITDY' is not of type 'object'", "'IT.LB.LBDTC' is not of type 'object'", "'IT.LB.LBDY' is not of type 'object'", "'IT.LB.STUDYID' is not of type 'object'", "'IT.LB.USUBJID' is not of type 'object'", "'IT.LB.STUDYID' is not of type 'object'", "'IT.LB.DOMAIN' is not of type 'object'", "'IT.LB.USUBJID' is not of type 'object'", "'IT.LB.LBSEQ' is not of type 'object'", "'IT.LB.LBTESTCD' is not of type 'object'", "'IT.LB.LBTEST' is not of type 'object'", "'IT.LB.LBCAT' is not of type 'object'", "'IT.LB.LBORRES' is not of type 'object'", "'IT.LB.LBORRESU' is not of type 'object'", "'IT.LB.LBORNRLO' is not of type 'object'", "'IT.LB.LBORNRHI' is not of type 'object'", "'IT.LB.LBSTRESC' is not of type 'object'", "'IT.LB.LBSTRESN' is not of type 'object'", "'IT.LB.LBSTRESU' is not of type 'object'", "'IT.LB.LBSTNRLO' is not of type 'object'", "'IT.LB.LBSTNRHI' is not of type 'object'", "'IT.LB.LBNRIND' is not of type 'object'", "'IT.LB.LBBLFL' is not of type 'object'", "'IT.LB.VISITNUM' is not of type 'object'", "'IT.LB.VISIT' is not of type 'object'", "'IT.LB.VISITDY' is not of type 'object'", "'IT.LB.LBDTC' is not of type 'object'", "'IT.LB.LBDY' is not of type 'object'", "'IT.LB.STUDYID' is not of type 'object'", "'IT.LB.USUBJID' is not of type 'object'"] source=&lt;ValidationError: "{'OID': 'IG.LB', 'name': 'LB', 'description': 'Laboratory Test Findings', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.LB.STUDYID', 'IT.LB.DOMAIN', 'IT.LB.USUBJID', 'IT.LB.LBSEQ', 'IT.LB.LBTESTCD', 'IT.LB.LBTEST', 'IT.LB.LBCAT', 'IT.LB.LBORRES', 'IT.LB.LBORRESU', 'IT.LB.LBORNRLO', 'IT.LB.LBORNRHI', 'IT.LB.LBSTRESC', 'IT.LB.LBSTRESN', 'IT.LB.LBSTRESU', 'IT.LB.LBSTNRLO', 'IT.LB.LBSTNRHI', 'IT.LB.LBNRIND', 'IT.LB.LBBLFL', 'IT.LB.VISITNUM', 'IT.LB.VISIT', 'IT.LB.VISITDY', 'IT.LB.LBDTC', 'IT.LB.LBDY'], 'keySequence': ['IT.LB.STUDYID', 'IT.LB.USUBJID']} is not valid under any of the given schemas"&gt;</t>
+          <t>'OID' is a required property in /items/108/origin/documents/0</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>type='jsonschema validation' severity=&lt;Severity.ERROR: 'ERROR'&gt; message="{'OID': 'IG.AE', 'name': 'AE', 'description': 'Adverse Events', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.AE.STUDYID', 'IT.AE.DOMAIN', 'IT.AE.USUBJID', 'IT.AE.AESEQ', 'IT.AE.AESPID', 'IT.AE.AETERM', 'IT.AE.AELLT', 'IT.AE.AELLTCD', 'IT.AE.AEDECOD', 'IT.AE.AEPTCD', 'IT.AE.AEHLT', 'IT.AE.AEHLTCD', 'IT.AE.AEHLGT', 'IT.AE.AEHLGTCD', 'IT.AE.AEBODSYS', 'IT.AE.AEBDSYCD', 'IT.AE.AESOC', 'IT.AE.AESOCCD', 'IT.AE.AESEV', 'IT.AE.AESER', 'IT.AE.AEACN', 'IT.AE.AEREL', 'IT.AE.AEOUT', 'IT.AE.AESCAN', 'IT.AE.AESCONG', 'IT.AE.AESDISAB', 'IT.AE.AESDTH', 'IT.AE.AESHOSP', 'IT.AE.AESLIFE', 'IT.AE.AESOD', 'IT.AE.AEDTC', 'IT.AE.AESTDTC', 'IT.AE.AEENDTC', 'IT.AE.AESTDY', 'IT.AE.AEENDY'], 'keySequence': ['IT.AE.STUDYID', 'IT.AE.USUBJID']} is not valid under any of the given schemas in /itemGroups/2" instance={'OID': 'MDV.360i CDISC PILOT - LZZT', 'name': 'MDV 360i CDISC PILOT - LZZT', 'description': 'Data Definitions for 360i CDISC PILOT - LZZT', 'fileOID': 'ODM.DEFINE-360I.360i CDISC PILOT - LZZT', 'creationDateTime': '2026-04-15T20:36:55.421402+00:00', 'odmVersion': '1.3.2', 'fileType': 'Snapshot', 'originator': 'Define-360i Processor', 'context': 'Other', 'defineVersion': '2.1.0', 'studyOID': '', 'studyName': '360i CDISC PILOT - LZZT', 'studyDescription': "Safety and Efficacy of the Xanomeline Transdermal Therapeutic System (TTS) in Patients with Mild to Moderate Alzheimer's Disease", 'protocolName': '360i LZZT Xanomeline (LY246708)', 'itemGroups': [{'OID': 'IG.SC', 'name': 'SC', 'description': 'Subject Characteristics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SC.STUDYID', 'IT.SC.DOMAIN', 'IT.SC.USUBJID', 'IT.SC.SCSEQ', 'IT.SC.SCTESTCD', 'IT.SC.SCTEST', 'IT.SC.SCCAT', 'IT.SC.SCORRES', 'IT.SC.SCORRESU', 'IT.SC.SCSTRESC', 'IT.SC.SCSTRESN', 'IT.SC.SCSTRESU', 'IT.SC.SCDTC', 'IT.SC.SCDY'], 'keySequence': ['IT.SC.STUDYID', 'IT.SC.USUBJID']}, {'OID': 'IG.LB', 'name': 'LB', 'description': 'Laboratory Test Findings', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.LB.STUDYID', 'IT.LB.DOMAIN', 'IT.LB.USUBJID', 'IT.LB.LBSEQ', 'IT.LB.LBTESTCD', 'IT.LB.LBTEST', 'IT.LB.LBCAT', 'IT.LB.LBORRES', 'IT.LB.LBORRESU', 'IT.LB.LBORNRLO', 'IT.LB.LBORNRHI', 'IT.LB.LBSTRESC', 'IT.LB.LBSTRESN', 'IT.LB.LBSTRESU', 'IT.LB.LBSTNRLO', 'IT.LB.LBSTNRHI', 'IT.LB.LBNRIND', 'IT.LB.LBBLFL', 'IT.LB.VISITNUM', 'IT.LB.VISIT', 'IT.LB.VISITDY', 'IT.LB.LBDTC', 'IT.LB.LBDY'], 'keySequence': ['IT.LB.STUDYID', 'IT.LB.USUBJID']}, {'OID': 'IG.AE', 'name': 'AE', 'description': 'Adverse Events', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.AE.STUDYID', 'IT.AE.DOMAIN', 'IT.AE.USUBJID', 'IT.AE.AESEQ', 'IT.AE.AESPID', 'IT.AE.AETERM', 'IT.AE.AELLT', 'IT.AE.AELLTCD', 'IT.AE.AEDECOD', 'IT.AE.AEPTCD', 'IT.AE.AEHLT', 'IT.AE.AEHLTCD', 'IT.AE.AEHLGT', 'IT.AE.AEHLGTCD', 'IT.AE.AEBODSYS', 'IT.AE.AEBDSYCD', 'IT.AE.AESOC', 'IT.AE.AESOCCD', 'IT.AE.AESEV', 'IT.AE.AESER', 'IT.AE.AEACN', 'IT.AE.AEREL', 'IT.AE.AEOUT', 'IT.AE.AESCAN', 'IT.AE.AESCONG', 'IT.AE.AESDISAB', 'IT.AE.AESDTH', 'IT.AE.AESHOSP', 'IT.AE.AESLIFE', 'IT.AE.AESOD', 'IT.AE.AEDTC', 'IT.AE.AESTDTC', 'IT.AE.AEENDTC', 'IT.AE.AESTDY', 'IT.AE.AEENDY'], 'keySequence': ['IT.AE.STUDYID', 'IT.AE.USUBJID']}, {'OID': 'IG.QS', 'name': 'QS', 'description': 'Questionnaires', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.QS.STUDYID', 'IT.QS.DOMAIN', 'IT.QS.USUBJID', 'IT.QS.QSSEQ', 'IT.QS.QSTESTCD', 'IT.QS.QSTEST', 'IT.QS.QSCAT', 'IT.QS.QSSCAT', 'IT.QS.QSORRES', 'IT.QS.QSORRESU', 'IT.QS.QSSTRESC', 'IT.QS.QSSTRESN', 'IT.QS.QSSTRESU', 'IT.QS.QSBLFL', 'IT.QS.QSDRVFL', 'IT.QS.VISITNUM', 'IT.QS.VISIT', 'IT.QS.VISITDY', 'IT.QS.QSDTC', 'IT.QS.QSDY'], 'keySequence': ['IT.QS.STUDYID', 'IT.QS.USUBJID']}, {'OID': 'IG.DM', 'name': 'DM', 'description': 'Demographics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DM.STUDYID', 'IT.DM.SITEID', 'IT.DM.DOMAIN', 'IT.DM.USUBJID', 'IT.DM.SUBJID', 'IT.DM.RFSTDTC', 'IT.DM.RFENDTC', 'IT.DM.RFXSTDTC', 'IT.DM.RFXENDTC', 'IT.DM.RFICDTC', 'IT.DM.RFPENDTC', 'IT.DM.DTHDTC', 'IT.DM.DTHFL', 'IT.DM.AGE', 'IT.DM.AGEU', 'IT.DM.SEX', 'IT.DM.RACE', 'IT.DM.ETHNIC', 'IT.DM.COUNTRY', 'IT.DM.ARM', 'IT.DM.ARMCD', 'IT.DM.ACTARM', 'IT.DM.ACTARMCD', 'IT.DM.DMDTC', 'IT.DM.DMDY'], 'keySequence': ['IT.DM.STUDYID', 'IT.DM.USUBJID']}, {'OID': 'IG.CM', 'name': 'CM', 'description': 'Concomitant Medications', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.CM.STUDYID', 'IT.CM.DOMAIN', 'IT.CM.USUBJID', 'IT.CM.CMSEQ', 'IT.CM.CMSPID', 'IT.CM.CMTRT', 'IT.CM.CMDECOD', 'IT.CM.CMINDC', 'IT.CM.CMCLAS', 'IT.CM.CMDOSE', 'IT.CM.CMDOSU', 'IT.CM.CMDOSFRQ', 'IT.CM.CMROUTE', 'IT.CM.VISITNUM', 'IT.CM.VISIT', 'IT.CM.VISITDY', 'IT.CM.CMDTC', 'IT.CM.CMSTDTC', 'IT.CM.CMENDTC', 'IT.CM.CMSTDY', 'IT.CM.CMENDY'], 'keySequence': ['IT.CM.STUDYID', 'IT.CM.USUBJID']}, {'OID': 'IG.SUPPDS', 'name': 'SUPPDS', 'description': 'Supplemental Qualifiers for DS', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.RDOMAIN', 'IT.SUPPDS.USUBJID', 'IT.SUPPDS.IDVAR', 'IT.SUPPDS.IDVARVAL', 'IT.SUPPDS.QNAM', 'IT.SUPPDS.QLABEL', 'IT.SUPPDS.QVAL', 'IT.SUPPDS.QORIG', 'IT.SUPPDS.QEVAL'], 'keySequence': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.USUBJID']}, {'OID': 'IG.EX', 'name': 'EX', 'description': 'Exposure', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.EX.STUDYID', 'IT.EX.DOMAIN', 'IT.EX.USUBJID', 'IT.EX.EXSEQ', 'IT.EX.EXTRT', 'IT.EX.EXDOSE', 'IT.EX.EXDOSU', 'IT.EX.EXDOSFRM', 'IT.EX.EXDOSFRQ', 'IT.EX.EXROUTE', 'IT.EX.VISITNUM', 'IT.EX.VISIT', 'IT.EX.VISITDY', 'IT.EX.EXSTDTC', 'IT.EX.EXENDTC', 'IT.EX.EXSTDY', 'IT.EX.EXENDY'], 'keySequence': ['IT.EX.STUDYID', 'IT.EX.USUBJID']}, {'OID': 'IG.VS', 'name': 'VS', 'description': 'Vital Signs', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.VS.STUDYID', 'IT.VS.DOMAIN', 'IT.VS.USUBJID', 'IT.VS.VSSEQ', 'IT.VS.VSTESTCD', 'IT.VS.VSTEST', 'IT.VS.VSPOS', 'IT.VS.VSORRES', 'IT.VS.VSORRESU', 'IT.VS.VSSTRESC', 'IT.VS.VSSTRESN', 'IT.VS.VSSTRESU', 'IT.VS.VSSTAT', 'IT.VS.VSLOC', 'IT.VS.VSBLFL', 'IT.VS.VISITNUM', 'IT.VS.VISIT', 'IT.VS.VISITDY', 'IT.VS.VSDTC', 'IT.VS.VSDY', 'IT.VS.VSTPT', 'IT.VS.VSTPTNUM', 'IT.VS.VSELTM', 'IT.VS.VSTPTREF'], 'keySequence': ['IT.VS.STUDYID', 'IT.VS.USUBJID']}, {'OID': 'IG.MH', 'name': 'MH', 'description': 'Medical History', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.MH.STUDYID', 'IT.MH.DOMAIN', 'IT.MH.USUBJID', 'IT.MH.MHSEQ', 'IT.MH.MHSPID', 'IT.MH.MHTERM', 'IT.MH.MHLLT', 'IT.MH.MHDECOD', 'IT.MH.MHHLT', 'IT.MH.MHHLGT', 'IT.MH.MHCAT', 'IT.MH.MHBODSYS', 'IT.MH.MHSEV', 'IT.MH.VISITNUM', 'IT.MH.VISIT', 'IT.MH.VISITDY', 'IT.MH.MHDTC', 'IT.MH.MHSTDTC', 'IT.MH.MHDY'], 'keySequence': ['IT.MH.STUDYID', 'IT.MH.USUBJID']}, {'OID': 'IG.DS', 'name': 'DS', 'description': 'Disposition', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DS.STUDYID', 'IT.DS.DOMAIN', 'IT.DS.USUBJID', 'IT.DS.DSSEQ', 'IT.DS.DSSPID', 'IT.DS.DSTERM', 'IT.DS.DSDECOD', 'IT.DS.DSCAT', 'IT.DS.VISITNUM', 'IT.DS.VISIT', 'IT.DS.DSDTC', 'IT.DS.DSSTDTC', 'IT.DS.DSSTDY'], 'keySequence': ['IT.DS.STUDYID', 'IT.DS.USUBJID']}], 'standards': [{'OID': 'STD.1', 'name': 'SDTMIG', 'type': 'IG', 'version': '3.4', 'status': 'Final'}, {'OID': 'STD.2', 'name': 'CDISC/NCI', 'type': 'CT', 'version': '2024-09-27', 'status': 'Final'}]} instance_index=0 instantiates='MetaDataVersion' context=["'IT.AE.STUDYID' is not of type 'object'", "'IT.AE.DOMAIN' is not of type 'object'", "'IT.AE.USUBJID' is not of type 'object'", "'IT.AE.AESEQ' is not of type 'object'", "'IT.AE.AESPID' is not of type 'object'", "'IT.AE.AETERM' is not of type 'object'", "'IT.AE.AELLT' is not of type 'object'", "'IT.AE.AELLTCD' is not of type 'object'", "'IT.AE.AEDECOD' is not of type 'object'", "'IT.AE.AEPTCD' is not of type 'object'", "'IT.AE.AEHLT' is not of type 'object'", "'IT.AE.AEHLTCD' is not of type 'object'", "'IT.AE.AEHLGT' is not of type 'object'", "'IT.AE.AEHLGTCD' is not of type 'object'", "'IT.AE.AEBODSYS' is not of type 'object'", "'IT.AE.AEBDSYCD' is not of type 'object'", "'IT.AE.AESOC' is not of type 'object'", "'IT.AE.AESOCCD' is not of type 'object'", "'IT.AE.AESEV' is not of type 'object'", "'IT.AE.AESER' is not of type 'object'", "'IT.AE.AEACN' is not of type 'object'", "'IT.AE.AEREL' is not of type 'object'", "'IT.AE.AEOUT' is not of type 'object'", "'IT.AE.AESCAN' is not of type 'object'", "'IT.AE.AESCONG' is not of type 'object'", "'IT.AE.AESDISAB' is not of type 'object'", "'IT.AE.AESDTH' is not of type 'object'", "'IT.AE.AESHOSP' is not of type 'object'", "'IT.AE.AESLIFE' is not of type 'object'", "'IT.AE.AESOD' is not of type 'object'", "'IT.AE.AEDTC' is not of type 'object'", "'IT.AE.AESTDTC' is not of type 'object'", "'IT.AE.AEENDTC' is not of type 'object'", "'IT.AE.AESTDY' is not of type 'object'", "'IT.AE.AEENDY' is not of type 'object'", "'IT.AE.STUDYID' is not of type 'object'", "'IT.AE.USUBJID' is not of type 'object'", "'IT.AE.STUDYID' is not of type 'object'", "'IT.AE.DOMAIN' is not of type 'object'", "'IT.AE.USUBJID' is not of type 'object'", "'IT.AE.AESEQ' is not of type 'object'", "'IT.AE.AESPID' is not of type 'object'", "'IT.AE.AETERM' is not of type 'object'", "'IT.AE.AELLT' is not of type 'object'", "'IT.AE.AELLTCD' is not of type 'object'", "'IT.AE.AEDECOD' is not of type 'object'", "'IT.AE.AEPTCD' is not of type 'object'", "'IT.AE.AEHLT' is not of type 'object'", "'IT.AE.AEHLTCD' is not of type 'object'", "'IT.AE.AEHLGT' is not of type 'object'", "'IT.AE.AEHLGTCD' is not of type 'object'", "'IT.AE.AEBODSYS' is not of type 'object'", "'IT.AE.AEBDSYCD' is not of type 'object'", "'IT.AE.AESOC' is not of type 'object'", "'IT.AE.AESOCCD' is not of type 'object'", "'IT.AE.AESEV' is not of type 'object'", "'IT.AE.AESER' is not of type 'object'", "'IT.AE.AEACN' is not of type 'object'", "'IT.AE.AEREL' is not of type 'object'", "'IT.AE.AEOUT' is not of type 'object'", "'IT.AE.AESCAN' is not of type 'object'", "'IT.AE.AESCONG' is not of type 'object'", "'IT.AE.AESDISAB' is not of type 'object'", "'IT.AE.AESDTH' is not of type 'object'", "'IT.AE.AESHOSP' is not of type 'object'", "'IT.AE.AESLIFE' is not of type 'object'", "'IT.AE.AESOD' is not of type 'object'", "'IT.AE.AEDTC' is not of type 'object'", "'IT.AE.AESTDTC' is not of type 'object'", "'IT.AE.AEENDTC' is not of type 'object'", "'IT.AE.AESTDY' is not of type 'object'", "'IT.AE.AEENDY' is not of type 'object'", "'IT.AE.STUDYID' is not of type 'object'", "'IT.AE.USUBJID' is not of type 'object'"] source=&lt;ValidationError: "{'OID': 'IG.AE', 'name': 'AE', 'description': 'Adverse Events', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.AE.STUDYID', 'IT.AE.DOMAIN', 'IT.AE.USUBJID', 'IT.AE.AESEQ', 'IT.AE.AESPID', 'IT.AE.AETERM', 'IT.AE.AELLT', 'IT.AE.AELLTCD', 'IT.AE.AEDECOD', 'IT.AE.AEPTCD', 'IT.AE.AEHLT', 'IT.AE.AEHLTCD', 'IT.AE.AEHLGT', 'IT.AE.AEHLGTCD', 'IT.AE.AEBODSYS', 'IT.AE.AEBDSYCD', 'IT.AE.AESOC', 'IT.AE.AESOCCD', 'IT.AE.AESEV', 'IT.AE.AESER', 'IT.AE.AEACN', 'IT.AE.AEREL', 'IT.AE.AEOUT', 'IT.AE.AESCAN', 'IT.AE.AESCONG', 'IT.AE.AESDISAB', 'IT.AE.AESDTH', 'IT.AE.AESHOSP', 'IT.AE.AESLIFE', 'IT.AE.AESOD', 'IT.AE.AEDTC', 'IT.AE.AESTDTC', 'IT.AE.AEENDTC', 'IT.AE.AESTDY', 'IT.AE.AEENDY'], 'keySequence': ['IT.AE.STUDYID', 'IT.AE.USUBJID']} is not valid under any of the given schemas"&gt;</t>
+          <t>'OID' is a required property in /items/171/origin/documents/0</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>type='jsonschema validation' severity=&lt;Severity.ERROR: 'ERROR'&gt; message="{'OID': 'IG.QS', 'name': 'QS', 'description': 'Questionnaires', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.QS.STUDYID', 'IT.QS.DOMAIN', 'IT.QS.USUBJID', 'IT.QS.QSSEQ', 'IT.QS.QSTESTCD', 'IT.QS.QSTEST', 'IT.QS.QSCAT', 'IT.QS.QSSCAT', 'IT.QS.QSORRES', 'IT.QS.QSORRESU', 'IT.QS.QSSTRESC', 'IT.QS.QSSTRESN', 'IT.QS.QSSTRESU', 'IT.QS.QSBLFL', 'IT.QS.QSDRVFL', 'IT.QS.VISITNUM', 'IT.QS.VISIT', 'IT.QS.VISITDY', 'IT.QS.QSDTC', 'IT.QS.QSDY'], 'keySequence': ['IT.QS.STUDYID', 'IT.QS.USUBJID']} is not valid under any of the given schemas in /itemGroups/3" instance={'OID': 'MDV.360i CDISC PILOT - LZZT', 'name': 'MDV 360i CDISC PILOT - LZZT', 'description': 'Data Definitions for 360i CDISC PILOT - LZZT', 'fileOID': 'ODM.DEFINE-360I.360i CDISC PILOT - LZZT', 'creationDateTime': '2026-04-15T20:36:55.421402+00:00', 'odmVersion': '1.3.2', 'fileType': 'Snapshot', 'originator': 'Define-360i Processor', 'context': 'Other', 'defineVersion': '2.1.0', 'studyOID': '', 'studyName': '360i CDISC PILOT - LZZT', 'studyDescription': "Safety and Efficacy of the Xanomeline Transdermal Therapeutic System (TTS) in Patients with Mild to Moderate Alzheimer's Disease", 'protocolName': '360i LZZT Xanomeline (LY246708)', 'itemGroups': [{'OID': 'IG.SC', 'name': 'SC', 'description': 'Subject Characteristics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SC.STUDYID', 'IT.SC.DOMAIN', 'IT.SC.USUBJID', 'IT.SC.SCSEQ', 'IT.SC.SCTESTCD', 'IT.SC.SCTEST', 'IT.SC.SCCAT', 'IT.SC.SCORRES', 'IT.SC.SCORRESU', 'IT.SC.SCSTRESC', 'IT.SC.SCSTRESN', 'IT.SC.SCSTRESU', 'IT.SC.SCDTC', 'IT.SC.SCDY'], 'keySequence': ['IT.SC.STUDYID', 'IT.SC.USUBJID']}, {'OID': 'IG.LB', 'name': 'LB', 'description': 'Laboratory Test Findings', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.LB.STUDYID', 'IT.LB.DOMAIN', 'IT.LB.USUBJID', 'IT.LB.LBSEQ', 'IT.LB.LBTESTCD', 'IT.LB.LBTEST', 'IT.LB.LBCAT', 'IT.LB.LBORRES', 'IT.LB.LBORRESU', 'IT.LB.LBORNRLO', 'IT.LB.LBORNRHI', 'IT.LB.LBSTRESC', 'IT.LB.LBSTRESN', 'IT.LB.LBSTRESU', 'IT.LB.LBSTNRLO', 'IT.LB.LBSTNRHI', 'IT.LB.LBNRIND', 'IT.LB.LBBLFL', 'IT.LB.VISITNUM', 'IT.LB.VISIT', 'IT.LB.VISITDY', 'IT.LB.LBDTC', 'IT.LB.LBDY'], 'keySequence': ['IT.LB.STUDYID', 'IT.LB.USUBJID']}, {'OID': 'IG.AE', 'name': 'AE', 'description': 'Adverse Events', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.AE.STUDYID', 'IT.AE.DOMAIN', 'IT.AE.USUBJID', 'IT.AE.AESEQ', 'IT.AE.AESPID', 'IT.AE.AETERM', 'IT.AE.AELLT', 'IT.AE.AELLTCD', 'IT.AE.AEDECOD', 'IT.AE.AEPTCD', 'IT.AE.AEHLT', 'IT.AE.AEHLTCD', 'IT.AE.AEHLGT', 'IT.AE.AEHLGTCD', 'IT.AE.AEBODSYS', 'IT.AE.AEBDSYCD', 'IT.AE.AESOC', 'IT.AE.AESOCCD', 'IT.AE.AESEV', 'IT.AE.AESER', 'IT.AE.AEACN', 'IT.AE.AEREL', 'IT.AE.AEOUT', 'IT.AE.AESCAN', 'IT.AE.AESCONG', 'IT.AE.AESDISAB', 'IT.AE.AESDTH', 'IT.AE.AESHOSP', 'IT.AE.AESLIFE', 'IT.AE.AESOD', 'IT.AE.AEDTC', 'IT.AE.AESTDTC', 'IT.AE.AEENDTC', 'IT.AE.AESTDY', 'IT.AE.AEENDY'], 'keySequence': ['IT.AE.STUDYID', 'IT.AE.USUBJID']}, {'OID': 'IG.QS', 'name': 'QS', 'description': 'Questionnaires', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.QS.STUDYID', 'IT.QS.DOMAIN', 'IT.QS.USUBJID', 'IT.QS.QSSEQ', 'IT.QS.QSTESTCD', 'IT.QS.QSTEST', 'IT.QS.QSCAT', 'IT.QS.QSSCAT', 'IT.QS.QSORRES', 'IT.QS.QSORRESU', 'IT.QS.QSSTRESC', 'IT.QS.QSSTRESN', 'IT.QS.QSSTRESU', 'IT.QS.QSBLFL', 'IT.QS.QSDRVFL', 'IT.QS.VISITNUM', 'IT.QS.VISIT', 'IT.QS.VISITDY', 'IT.QS.QSDTC', 'IT.QS.QSDY'], 'keySequence': ['IT.QS.STUDYID', 'IT.QS.USUBJID']}, {'OID': 'IG.DM', 'name': 'DM', 'description': 'Demographics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DM.STUDYID', 'IT.DM.SITEID', 'IT.DM.DOMAIN', 'IT.DM.USUBJID', 'IT.DM.SUBJID', 'IT.DM.RFSTDTC', 'IT.DM.RFENDTC', 'IT.DM.RFXSTDTC', 'IT.DM.RFXENDTC', 'IT.DM.RFICDTC', 'IT.DM.RFPENDTC', 'IT.DM.DTHDTC', 'IT.DM.DTHFL', 'IT.DM.AGE', 'IT.DM.AGEU', 'IT.DM.SEX', 'IT.DM.RACE', 'IT.DM.ETHNIC', 'IT.DM.COUNTRY', 'IT.DM.ARM', 'IT.DM.ARMCD', 'IT.DM.ACTARM', 'IT.DM.ACTARMCD', 'IT.DM.DMDTC', 'IT.DM.DMDY'], 'keySequence': ['IT.DM.STUDYID', 'IT.DM.USUBJID']}, {'OID': 'IG.CM', 'name': 'CM', 'description': 'Concomitant Medications', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.CM.STUDYID', 'IT.CM.DOMAIN', 'IT.CM.USUBJID', 'IT.CM.CMSEQ', 'IT.CM.CMSPID', 'IT.CM.CMTRT', 'IT.CM.CMDECOD', 'IT.CM.CMINDC', 'IT.CM.CMCLAS', 'IT.CM.CMDOSE', 'IT.CM.CMDOSU', 'IT.CM.CMDOSFRQ', 'IT.CM.CMROUTE', 'IT.CM.VISITNUM', 'IT.CM.VISIT', 'IT.CM.VISITDY', 'IT.CM.CMDTC', 'IT.CM.CMSTDTC', 'IT.CM.CMENDTC', 'IT.CM.CMSTDY', 'IT.CM.CMENDY'], 'keySequence': ['IT.CM.STUDYID', 'IT.CM.USUBJID']}, {'OID': 'IG.SUPPDS', 'name': 'SUPPDS', 'description': 'Supplemental Qualifiers for DS', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.RDOMAIN', 'IT.SUPPDS.USUBJID', 'IT.SUPPDS.IDVAR', 'IT.SUPPDS.IDVARVAL', 'IT.SUPPDS.QNAM', 'IT.SUPPDS.QLABEL', 'IT.SUPPDS.QVAL', 'IT.SUPPDS.QORIG', 'IT.SUPPDS.QEVAL'], 'keySequence': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.USUBJID']}, {'OID': 'IG.EX', 'name': 'EX', 'description': 'Exposure', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.EX.STUDYID', 'IT.EX.DOMAIN', 'IT.EX.USUBJID', 'IT.EX.EXSEQ', 'IT.EX.EXTRT', 'IT.EX.EXDOSE', 'IT.EX.EXDOSU', 'IT.EX.EXDOSFRM', 'IT.EX.EXDOSFRQ', 'IT.EX.EXROUTE', 'IT.EX.VISITNUM', 'IT.EX.VISIT', 'IT.EX.VISITDY', 'IT.EX.EXSTDTC', 'IT.EX.EXENDTC', 'IT.EX.EXSTDY', 'IT.EX.EXENDY'], 'keySequence': ['IT.EX.STUDYID', 'IT.EX.USUBJID']}, {'OID': 'IG.VS', 'name': 'VS', 'description': 'Vital Signs', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.VS.STUDYID', 'IT.VS.DOMAIN', 'IT.VS.USUBJID', 'IT.VS.VSSEQ', 'IT.VS.VSTESTCD', 'IT.VS.VSTEST', 'IT.VS.VSPOS', 'IT.VS.VSORRES', 'IT.VS.VSORRESU', 'IT.VS.VSSTRESC', 'IT.VS.VSSTRESN', 'IT.VS.VSSTRESU', 'IT.VS.VSSTAT', 'IT.VS.VSLOC', 'IT.VS.VSBLFL', 'IT.VS.VISITNUM', 'IT.VS.VISIT', 'IT.VS.VISITDY', 'IT.VS.VSDTC', 'IT.VS.VSDY', 'IT.VS.VSTPT', 'IT.VS.VSTPTNUM', 'IT.VS.VSELTM', 'IT.VS.VSTPTREF'], 'keySequence': ['IT.VS.STUDYID', 'IT.VS.USUBJID']}, {'OID': 'IG.MH', 'name': 'MH', 'description': 'Medical History', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.MH.STUDYID', 'IT.MH.DOMAIN', 'IT.MH.USUBJID', 'IT.MH.MHSEQ', 'IT.MH.MHSPID', 'IT.MH.MHTERM', 'IT.MH.MHLLT', 'IT.MH.MHDECOD', 'IT.MH.MHHLT', 'IT.MH.MHHLGT', 'IT.MH.MHCAT', 'IT.MH.MHBODSYS', 'IT.MH.MHSEV', 'IT.MH.VISITNUM', 'IT.MH.VISIT', 'IT.MH.VISITDY', 'IT.MH.MHDTC', 'IT.MH.MHSTDTC', 'IT.MH.MHDY'], 'keySequence': ['IT.MH.STUDYID', 'IT.MH.USUBJID']}, {'OID': 'IG.DS', 'name': 'DS', 'description': 'Disposition', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DS.STUDYID', 'IT.DS.DOMAIN', 'IT.DS.USUBJID', 'IT.DS.DSSEQ', 'IT.DS.DSSPID', 'IT.DS.DSTERM', 'IT.DS.DSDECOD', 'IT.DS.DSCAT', 'IT.DS.VISITNUM', 'IT.DS.VISIT', 'IT.DS.DSDTC', 'IT.DS.DSSTDTC', 'IT.DS.DSSTDY'], 'keySequence': ['IT.DS.STUDYID', 'IT.DS.USUBJID']}], 'standards': [{'OID': 'STD.1', 'name': 'SDTMIG', 'type': 'IG', 'version': '3.4', 'status': 'Final'}, {'OID': 'STD.2', 'name': 'CDISC/NCI', 'type': 'CT', 'version': '2024-09-27', 'status': 'Final'}]} instance_index=0 instantiates='MetaDataVersion' context=["'IT.QS.STUDYID' is not of type 'object'", "'IT.QS.DOMAIN' is not of type 'object'", "'IT.QS.USUBJID' is not of type 'object'", "'IT.QS.QSSEQ' is not of type 'object'", "'IT.QS.QSTESTCD' is not of type 'object'", "'IT.QS.QSTEST' is not of type 'object'", "'IT.QS.QSCAT' is not of type 'object'", "'IT.QS.QSSCAT' is not of type 'object'", "'IT.QS.QSORRES' is not of type 'object'", "'IT.QS.QSORRESU' is not of type 'object'", "'IT.QS.QSSTRESC' is not of type 'object'", "'IT.QS.QSSTRESN' is not of type 'object'", "'IT.QS.QSSTRESU' is not of type 'object'", "'IT.QS.QSBLFL' is not of type 'object'", "'IT.QS.QSDRVFL' is not of type 'object'", "'IT.QS.VISITNUM' is not of type 'object'", "'IT.QS.VISIT' is not of type 'object'", "'IT.QS.VISITDY' is not of type 'object'", "'IT.QS.QSDTC' is not of type 'object'", "'IT.QS.QSDY' is not of type 'object'", "'IT.QS.STUDYID' is not of type 'object'", "'IT.QS.USUBJID' is not of type 'object'", "'IT.QS.STUDYID' is not of type 'object'", "'IT.QS.DOMAIN' is not of type 'object'", "'IT.QS.USUBJID' is not of type 'object'", "'IT.QS.QSSEQ' is not of type 'object'", "'IT.QS.QSTESTCD' is not of type 'object'", "'IT.QS.QSTEST' is not of type 'object'", "'IT.QS.QSCAT' is not of type 'object'", "'IT.QS.QSSCAT' is not of type 'object'", "'IT.QS.QSORRES' is not of type 'object'", "'IT.QS.QSORRESU' is not of type 'object'", "'IT.QS.QSSTRESC' is not of type 'object'", "'IT.QS.QSSTRESN' is not of type 'object'", "'IT.QS.QSSTRESU' is not of type 'object'", "'IT.QS.QSBLFL' is not of type 'object'", "'IT.QS.QSDRVFL' is not of type 'object'", "'IT.QS.VISITNUM' is not of type 'object'", "'IT.QS.VISIT' is not of type 'object'", "'IT.QS.VISITDY' is not of type 'object'", "'IT.QS.QSDTC' is not of type 'object'", "'IT.QS.QSDY' is not of type 'object'", "'IT.QS.STUDYID' is not of type 'object'", "'IT.QS.USUBJID' is not of type 'object'"] source=&lt;ValidationError: "{'OID': 'IG.QS', 'name': 'QS', 'description': 'Questionnaires', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.QS.STUDYID', 'IT.QS.DOMAIN', 'IT.QS.USUBJID', 'IT.QS.QSSEQ', 'IT.QS.QSTESTCD', 'IT.QS.QSTEST', 'IT.QS.QSCAT', 'IT.QS.QSSCAT', 'IT.QS.QSORRES', 'IT.QS.QSORRESU', 'IT.QS.QSSTRESC', 'IT.QS.QSSTRESN', 'IT.QS.QSSTRESU', 'IT.QS.QSBLFL', 'IT.QS.QSDRVFL', 'IT.QS.VISITNUM', 'IT.QS.VISIT', 'IT.QS.VISITDY', 'IT.QS.QSDTC', 'IT.QS.QSDY'], 'keySequence': ['IT.QS.STUDYID', 'IT.QS.USUBJID']} is not valid under any of the given schemas"&gt;</t>
+          <t>'OID' is a required property in /items/173/origin/documents/0</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>type='jsonschema validation' severity=&lt;Severity.ERROR: 'ERROR'&gt; message="{'OID': 'IG.DM', 'name': 'DM', 'description': 'Demographics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DM.STUDYID', 'IT.DM.SITEID', 'IT.DM.DOMAIN', 'IT.DM.USUBJID', 'IT.DM.SUBJID', 'IT.DM.RFSTDTC', 'IT.DM.RFENDTC', 'IT.DM.RFXSTDTC', 'IT.DM.RFXENDTC', 'IT.DM.RFICDTC', 'IT.DM.RFPENDTC', 'IT.DM.DTHDTC', 'IT.DM.DTHFL', 'IT.DM.AGE', 'IT.DM.AGEU', 'IT.DM.SEX', 'IT.DM.RACE', 'IT.DM.ETHNIC', 'IT.DM.COUNTRY', 'IT.DM.ARM', 'IT.DM.ARMCD', 'IT.DM.ACTARM', 'IT.DM.ACTARMCD', 'IT.DM.DMDTC', 'IT.DM.DMDY'], 'keySequence': ['IT.DM.STUDYID', 'IT.DM.USUBJID']} is not valid under any of the given schemas in /itemGroups/4" instance={'OID': 'MDV.360i CDISC PILOT - LZZT', 'name': 'MDV 360i CDISC PILOT - LZZT', 'description': 'Data Definitions for 360i CDISC PILOT - LZZT', 'fileOID': 'ODM.DEFINE-360I.360i CDISC PILOT - LZZT', 'creationDateTime': '2026-04-15T20:36:55.421402+00:00', 'odmVersion': '1.3.2', 'fileType': 'Snapshot', 'originator': 'Define-360i Processor', 'context': 'Other', 'defineVersion': '2.1.0', 'studyOID': '', 'studyName': '360i CDISC PILOT - LZZT', 'studyDescription': "Safety and Efficacy of the Xanomeline Transdermal Therapeutic System (TTS) in Patients with Mild to Moderate Alzheimer's Disease", 'protocolName': '360i LZZT Xanomeline (LY246708)', 'itemGroups': [{'OID': 'IG.SC', 'name': 'SC', 'description': 'Subject Characteristics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SC.STUDYID', 'IT.SC.DOMAIN', 'IT.SC.USUBJID', 'IT.SC.SCSEQ', 'IT.SC.SCTESTCD', 'IT.SC.SCTEST', 'IT.SC.SCCAT', 'IT.SC.SCORRES', 'IT.SC.SCORRESU', 'IT.SC.SCSTRESC', 'IT.SC.SCSTRESN', 'IT.SC.SCSTRESU', 'IT.SC.SCDTC', 'IT.SC.SCDY'], 'keySequence': ['IT.SC.STUDYID', 'IT.SC.USUBJID']}, {'OID': 'IG.LB', 'name': 'LB', 'description': 'Laboratory Test Findings', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.LB.STUDYID', 'IT.LB.DOMAIN', 'IT.LB.USUBJID', 'IT.LB.LBSEQ', 'IT.LB.LBTESTCD', 'IT.LB.LBTEST', 'IT.LB.LBCAT', 'IT.LB.LBORRES', 'IT.LB.LBORRESU', 'IT.LB.LBORNRLO', 'IT.LB.LBORNRHI', 'IT.LB.LBSTRESC', 'IT.LB.LBSTRESN', 'IT.LB.LBSTRESU', 'IT.LB.LBSTNRLO', 'IT.LB.LBSTNRHI', 'IT.LB.LBNRIND', 'IT.LB.LBBLFL', 'IT.LB.VISITNUM', 'IT.LB.VISIT', 'IT.LB.VISITDY', 'IT.LB.LBDTC', 'IT.LB.LBDY'], 'keySequence': ['IT.LB.STUDYID', 'IT.LB.USUBJID']}, {'OID': 'IG.AE', 'name': 'AE', 'description': 'Adverse Events', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.AE.STUDYID', 'IT.AE.DOMAIN', 'IT.AE.USUBJID', 'IT.AE.AESEQ', 'IT.AE.AESPID', 'IT.AE.AETERM', 'IT.AE.AELLT', 'IT.AE.AELLTCD', 'IT.AE.AEDECOD', 'IT.AE.AEPTCD', 'IT.AE.AEHLT', 'IT.AE.AEHLTCD', 'IT.AE.AEHLGT', 'IT.AE.AEHLGTCD', 'IT.AE.AEBODSYS', 'IT.AE.AEBDSYCD', 'IT.AE.AESOC', 'IT.AE.AESOCCD', 'IT.AE.AESEV', 'IT.AE.AESER', 'IT.AE.AEACN', 'IT.AE.AEREL', 'IT.AE.AEOUT', 'IT.AE.AESCAN', 'IT.AE.AESCONG', 'IT.AE.AESDISAB', 'IT.AE.AESDTH', 'IT.AE.AESHOSP', 'IT.AE.AESLIFE', 'IT.AE.AESOD', 'IT.AE.AEDTC', 'IT.AE.AESTDTC', 'IT.AE.AEENDTC', 'IT.AE.AESTDY', 'IT.AE.AEENDY'], 'keySequence': ['IT.AE.STUDYID', 'IT.AE.USUBJID']}, {'OID': 'IG.QS', 'name': 'QS', 'description': 'Questionnaires', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.QS.STUDYID', 'IT.QS.DOMAIN', 'IT.QS.USUBJID', 'IT.QS.QSSEQ', 'IT.QS.QSTESTCD', 'IT.QS.QSTEST', 'IT.QS.QSCAT', 'IT.QS.QSSCAT', 'IT.QS.QSORRES', 'IT.QS.QSORRESU', 'IT.QS.QSSTRESC', 'IT.QS.QSSTRESN', 'IT.QS.QSSTRESU', 'IT.QS.QSBLFL', 'IT.QS.QSDRVFL', 'IT.QS.VISITNUM', 'IT.QS.VISIT', 'IT.QS.VISITDY', 'IT.QS.QSDTC', 'IT.QS.QSDY'], 'keySequence': ['IT.QS.STUDYID', 'IT.QS.USUBJID']}, {'OID': 'IG.DM', 'name': 'DM', 'description': 'Demographics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DM.STUDYID', 'IT.DM.SITEID', 'IT.DM.DOMAIN', 'IT.DM.USUBJID', 'IT.DM.SUBJID', 'IT.DM.RFSTDTC', 'IT.DM.RFENDTC', 'IT.DM.RFXSTDTC', 'IT.DM.RFXENDTC', 'IT.DM.RFICDTC', 'IT.DM.RFPENDTC', 'IT.DM.DTHDTC', 'IT.DM.DTHFL', 'IT.DM.AGE', 'IT.DM.AGEU', 'IT.DM.SEX', 'IT.DM.RACE', 'IT.DM.ETHNIC', 'IT.DM.COUNTRY', 'IT.DM.ARM', 'IT.DM.ARMCD', 'IT.DM.ACTARM', 'IT.DM.ACTARMCD', 'IT.DM.DMDTC', 'IT.DM.DMDY'], 'keySequence': ['IT.DM.STUDYID', 'IT.DM.USUBJID']}, {'OID': 'IG.CM', 'name': 'CM', 'description': 'Concomitant Medications', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.CM.STUDYID', 'IT.CM.DOMAIN', 'IT.CM.USUBJID', 'IT.CM.CMSEQ', 'IT.CM.CMSPID', 'IT.CM.CMTRT', 'IT.CM.CMDECOD', 'IT.CM.CMINDC', 'IT.CM.CMCLAS', 'IT.CM.CMDOSE', 'IT.CM.CMDOSU', 'IT.CM.CMDOSFRQ', 'IT.CM.CMROUTE', 'IT.CM.VISITNUM', 'IT.CM.VISIT', 'IT.CM.VISITDY', 'IT.CM.CMDTC', 'IT.CM.CMSTDTC', 'IT.CM.CMENDTC', 'IT.CM.CMSTDY', 'IT.CM.CMENDY'], 'keySequence': ['IT.CM.STUDYID', 'IT.CM.USUBJID']}, {'OID': 'IG.SUPPDS', 'name': 'SUPPDS', 'description': 'Supplemental Qualifiers for DS', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.RDOMAIN', 'IT.SUPPDS.USUBJID', 'IT.SUPPDS.IDVAR', 'IT.SUPPDS.IDVARVAL', 'IT.SUPPDS.QNAM', 'IT.SUPPDS.QLABEL', 'IT.SUPPDS.QVAL', 'IT.SUPPDS.QORIG', 'IT.SUPPDS.QEVAL'], 'keySequence': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.USUBJID']}, {'OID': 'IG.EX', 'name': 'EX', 'description': 'Exposure', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.EX.STUDYID', 'IT.EX.DOMAIN', 'IT.EX.USUBJID', 'IT.EX.EXSEQ', 'IT.EX.EXTRT', 'IT.EX.EXDOSE', 'IT.EX.EXDOSU', 'IT.EX.EXDOSFRM', 'IT.EX.EXDOSFRQ', 'IT.EX.EXROUTE', 'IT.EX.VISITNUM', 'IT.EX.VISIT', 'IT.EX.VISITDY', 'IT.EX.EXSTDTC', 'IT.EX.EXENDTC', 'IT.EX.EXSTDY', 'IT.EX.EXENDY'], 'keySequence': ['IT.EX.STUDYID', 'IT.EX.USUBJID']}, {'OID': 'IG.VS', 'name': 'VS', 'description': 'Vital Signs', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.VS.STUDYID', 'IT.VS.DOMAIN', 'IT.VS.USUBJID', 'IT.VS.VSSEQ', 'IT.VS.VSTESTCD', 'IT.VS.VSTEST', 'IT.VS.VSPOS', 'IT.VS.VSORRES', 'IT.VS.VSORRESU', 'IT.VS.VSSTRESC', 'IT.VS.VSSTRESN', 'IT.VS.VSSTRESU', 'IT.VS.VSSTAT', 'IT.VS.VSLOC', 'IT.VS.VSBLFL', 'IT.VS.VISITNUM', 'IT.VS.VISIT', 'IT.VS.VISITDY', 'IT.VS.VSDTC', 'IT.VS.VSDY', 'IT.VS.VSTPT', 'IT.VS.VSTPTNUM', 'IT.VS.VSELTM', 'IT.VS.VSTPTREF'], 'keySequence': ['IT.VS.STUDYID', 'IT.VS.USUBJID']}, {'OID': 'IG.MH', 'name': 'MH', 'description': 'Medical History', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.MH.STUDYID', 'IT.MH.DOMAIN', 'IT.MH.USUBJID', 'IT.MH.MHSEQ', 'IT.MH.MHSPID', 'IT.MH.MHTERM', 'IT.MH.MHLLT', 'IT.MH.MHDECOD', 'IT.MH.MHHLT', 'IT.MH.MHHLGT', 'IT.MH.MHCAT', 'IT.MH.MHBODSYS', 'IT.MH.MHSEV', 'IT.MH.VISITNUM', 'IT.MH.VISIT', 'IT.MH.VISITDY', 'IT.MH.MHDTC', 'IT.MH.MHSTDTC', 'IT.MH.MHDY'], 'keySequence': ['IT.MH.STUDYID', 'IT.MH.USUBJID']}, {'OID': 'IG.DS', 'name': 'DS', 'description': 'Disposition', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DS.STUDYID', 'IT.DS.DOMAIN', 'IT.DS.USUBJID', 'IT.DS.DSSEQ', 'IT.DS.DSSPID', 'IT.DS.DSTERM', 'IT.DS.DSDECOD', 'IT.DS.DSCAT', 'IT.DS.VISITNUM', 'IT.DS.VISIT', 'IT.DS.DSDTC', 'IT.DS.DSSTDTC', 'IT.DS.DSSTDY'], 'keySequence': ['IT.DS.STUDYID', 'IT.DS.USUBJID']}], 'standards': [{'OID': 'STD.1', 'name': 'SDTMIG', 'type': 'IG', 'version': '3.4', 'status': 'Final'}, {'OID': 'STD.2', 'name': 'CDISC/NCI', 'type': 'CT', 'version': '2024-09-27', 'status': 'Final'}]} instance_index=0 instantiates='MetaDataVersion' context=["'IT.DM.STUDYID' is not of type 'object'", "'IT.DM.SITEID' is not of type 'object'", "'IT.DM.DOMAIN' is not of type 'object'", "'IT.DM.USUBJID' is not of type 'object'", "'IT.DM.SUBJID' is not of type 'object'", "'IT.DM.RFSTDTC' is not of type 'object'", "'IT.DM.RFENDTC' is not of type 'object'", "'IT.DM.RFXSTDTC' is not of type 'object'", "'IT.DM.RFXENDTC' is not of type 'object'", "'IT.DM.RFICDTC' is not of type 'object'", "'IT.DM.RFPENDTC' is not of type 'object'", "'IT.DM.DTHDTC' is not of type 'object'", "'IT.DM.DTHFL' is not of type 'object'", "'IT.DM.AGE' is not of type 'object'", "'IT.DM.AGEU' is not of type 'object'", "'IT.DM.SEX' is not of type 'object'", "'IT.DM.RACE' is not of type 'object'", "'IT.DM.ETHNIC' is not of type 'object'", "'IT.DM.COUNTRY' is not of type 'object'", "'IT.DM.ARM' is not of type 'object'", "'IT.DM.ARMCD' is not of type 'object'", "'IT.DM.ACTARM' is not of type 'object'", "'IT.DM.ACTARMCD' is not of type 'object'", "'IT.DM.DMDTC' is not of type 'object'", "'IT.DM.DMDY' is not of type 'object'", "'IT.DM.STUDYID' is not of type 'object'", "'IT.DM.USUBJID' is not of type 'object'", "'IT.DM.STUDYID' is not of type 'object'", "'IT.DM.SITEID' is not of type 'object'", "'IT.DM.DOMAIN' is not of type 'object'", "'IT.DM.USUBJID' is not of type 'object'", "'IT.DM.SUBJID' is not of type 'object'", "'IT.DM.RFSTDTC' is not of type 'object'", "'IT.DM.RFENDTC' is not of type 'object'", "'IT.DM.RFXSTDTC' is not of type 'object'", "'IT.DM.RFXENDTC' is not of type 'object'", "'IT.DM.RFICDTC' is not of type 'object'", "'IT.DM.RFPENDTC' is not of type 'object'", "'IT.DM.DTHDTC' is not of type 'object'", "'IT.DM.DTHFL' is not of type 'object'", "'IT.DM.AGE' is not of type 'object'", "'IT.DM.AGEU' is not of type 'object'", "'IT.DM.SEX' is not of type 'object'", "'IT.DM.RACE' is not of type 'object'", "'IT.DM.ETHNIC' is not of type 'object'", "'IT.DM.COUNTRY' is not of type 'object'", "'IT.DM.ARM' is not of type 'object'", "'IT.DM.ARMCD' is not of type 'object'", "'IT.DM.ACTARM' is not of type 'object'", "'IT.DM.ACTARMCD' is not of type 'object'", "'IT.DM.DMDTC' is not of type 'object'", "'IT.DM.DMDY' is not of type 'object'", "'IT.DM.STUDYID' is not of type 'object'", "'IT.DM.USUBJID' is not of type 'object'"] source=&lt;ValidationError: "{'OID': 'IG.DM', 'name': 'DM', 'description': 'Demographics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DM.STUDYID', 'IT.DM.SITEID', 'IT.DM.DOMAIN', 'IT.DM.USUBJID', 'IT.DM.SUBJID', 'IT.DM.RFSTDTC', 'IT.DM.RFENDTC', 'IT.DM.RFXSTDTC', 'IT.DM.RFXENDTC', 'IT.DM.RFICDTC', 'IT.DM.RFPENDTC', 'IT.DM.DTHDTC', 'IT.DM.DTHFL', 'IT.DM.AGE', 'IT.DM.AGEU', 'IT.DM.SEX', 'IT.DM.RACE', 'IT.DM.ETHNIC', 'IT.DM.COUNTRY', 'IT.DM.ARM', 'IT.DM.ARMCD', 'IT.DM.ACTARM', 'IT.DM.ACTARMCD', 'IT.DM.DMDTC', 'IT.DM.DMDY'], 'keySequence': ['IT.DM.STUDYID', 'IT.DM.USUBJID']} is not valid under any of the given schemas"&gt;</t>
+          <t>'OID' is a required property in /items/174/origin/documents/0</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>type='jsonschema validation' severity=&lt;Severity.ERROR: 'ERROR'&gt; message="{'OID': 'IG.CM', 'name': 'CM', 'description': 'Concomitant Medications', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.CM.STUDYID', 'IT.CM.DOMAIN', 'IT.CM.USUBJID', 'IT.CM.CMSEQ', 'IT.CM.CMSPID', 'IT.CM.CMTRT', 'IT.CM.CMDECOD', 'IT.CM.CMINDC', 'IT.CM.CMCLAS', 'IT.CM.CMDOSE', 'IT.CM.CMDOSU', 'IT.CM.CMDOSFRQ', 'IT.CM.CMROUTE', 'IT.CM.VISITNUM', 'IT.CM.VISIT', 'IT.CM.VISITDY', 'IT.CM.CMDTC', 'IT.CM.CMSTDTC', 'IT.CM.CMENDTC', 'IT.CM.CMSTDY', 'IT.CM.CMENDY'], 'keySequence': ['IT.CM.STUDYID', 'IT.CM.USUBJID']} is not valid under any of the given schemas in /itemGroups/5" instance={'OID': 'MDV.360i CDISC PILOT - LZZT', 'name': 'MDV 360i CDISC PILOT - LZZT', 'description': 'Data Definitions for 360i CDISC PILOT - LZZT', 'fileOID': 'ODM.DEFINE-360I.360i CDISC PILOT - LZZT', 'creationDateTime': '2026-04-15T20:36:55.421402+00:00', 'odmVersion': '1.3.2', 'fileType': 'Snapshot', 'originator': 'Define-360i Processor', 'context': 'Other', 'defineVersion': '2.1.0', 'studyOID': '', 'studyName': '360i CDISC PILOT - LZZT', 'studyDescription': "Safety and Efficacy of the Xanomeline Transdermal Therapeutic System (TTS) in Patients with Mild to Moderate Alzheimer's Disease", 'protocolName': '360i LZZT Xanomeline (LY246708)', 'itemGroups': [{'OID': 'IG.SC', 'name': 'SC', 'description': 'Subject Characteristics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SC.STUDYID', 'IT.SC.DOMAIN', 'IT.SC.USUBJID', 'IT.SC.SCSEQ', 'IT.SC.SCTESTCD', 'IT.SC.SCTEST', 'IT.SC.SCCAT', 'IT.SC.SCORRES', 'IT.SC.SCORRESU', 'IT.SC.SCSTRESC', 'IT.SC.SCSTRESN', 'IT.SC.SCSTRESU', 'IT.SC.SCDTC', 'IT.SC.SCDY'], 'keySequence': ['IT.SC.STUDYID', 'IT.SC.USUBJID']}, {'OID': 'IG.LB', 'name': 'LB', 'description': 'Laboratory Test Findings', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.LB.STUDYID', 'IT.LB.DOMAIN', 'IT.LB.USUBJID', 'IT.LB.LBSEQ', 'IT.LB.LBTESTCD', 'IT.LB.LBTEST', 'IT.LB.LBCAT', 'IT.LB.LBORRES', 'IT.LB.LBORRESU', 'IT.LB.LBORNRLO', 'IT.LB.LBORNRHI', 'IT.LB.LBSTRESC', 'IT.LB.LBSTRESN', 'IT.LB.LBSTRESU', 'IT.LB.LBSTNRLO', 'IT.LB.LBSTNRHI', 'IT.LB.LBNRIND', 'IT.LB.LBBLFL', 'IT.LB.VISITNUM', 'IT.LB.VISIT', 'IT.LB.VISITDY', 'IT.LB.LBDTC', 'IT.LB.LBDY'], 'keySequence': ['IT.LB.STUDYID', 'IT.LB.USUBJID']}, {'OID': 'IG.AE', 'name': 'AE', 'description': 'Adverse Events', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.AE.STUDYID', 'IT.AE.DOMAIN', 'IT.AE.USUBJID', 'IT.AE.AESEQ', 'IT.AE.AESPID', 'IT.AE.AETERM', 'IT.AE.AELLT', 'IT.AE.AELLTCD', 'IT.AE.AEDECOD', 'IT.AE.AEPTCD', 'IT.AE.AEHLT', 'IT.AE.AEHLTCD', 'IT.AE.AEHLGT', 'IT.AE.AEHLGTCD', 'IT.AE.AEBODSYS', 'IT.AE.AEBDSYCD', 'IT.AE.AESOC', 'IT.AE.AESOCCD', 'IT.AE.AESEV', 'IT.AE.AESER', 'IT.AE.AEACN', 'IT.AE.AEREL', 'IT.AE.AEOUT', 'IT.AE.AESCAN', 'IT.AE.AESCONG', 'IT.AE.AESDISAB', 'IT.AE.AESDTH', 'IT.AE.AESHOSP', 'IT.AE.AESLIFE', 'IT.AE.AESOD', 'IT.AE.AEDTC', 'IT.AE.AESTDTC', 'IT.AE.AEENDTC', 'IT.AE.AESTDY', 'IT.AE.AEENDY'], 'keySequence': ['IT.AE.STUDYID', 'IT.AE.USUBJID']}, {'OID': 'IG.QS', 'name': 'QS', 'description': 'Questionnaires', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.QS.STUDYID', 'IT.QS.DOMAIN', 'IT.QS.USUBJID', 'IT.QS.QSSEQ', 'IT.QS.QSTESTCD', 'IT.QS.QSTEST', 'IT.QS.QSCAT', 'IT.QS.QSSCAT', 'IT.QS.QSORRES', 'IT.QS.QSORRESU', 'IT.QS.QSSTRESC', 'IT.QS.QSSTRESN', 'IT.QS.QSSTRESU', 'IT.QS.QSBLFL', 'IT.QS.QSDRVFL', 'IT.QS.VISITNUM', 'IT.QS.VISIT', 'IT.QS.VISITDY', 'IT.QS.QSDTC', 'IT.QS.QSDY'], 'keySequence': ['IT.QS.STUDYID', 'IT.QS.USUBJID']}, {'OID': 'IG.DM', 'name': 'DM', 'description': 'Demographics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DM.STUDYID', 'IT.DM.SITEID', 'IT.DM.DOMAIN', 'IT.DM.USUBJID', 'IT.DM.SUBJID', 'IT.DM.RFSTDTC', 'IT.DM.RFENDTC', 'IT.DM.RFXSTDTC', 'IT.DM.RFXENDTC', 'IT.DM.RFICDTC', 'IT.DM.RFPENDTC', 'IT.DM.DTHDTC', 'IT.DM.DTHFL', 'IT.DM.AGE', 'IT.DM.AGEU', 'IT.DM.SEX', 'IT.DM.RACE', 'IT.DM.ETHNIC', 'IT.DM.COUNTRY', 'IT.DM.ARM', 'IT.DM.ARMCD', 'IT.DM.ACTARM', 'IT.DM.ACTARMCD', 'IT.DM.DMDTC', 'IT.DM.DMDY'], 'keySequence': ['IT.DM.STUDYID', 'IT.DM.USUBJID']}, {'OID': 'IG.CM', 'name': 'CM', 'description': 'Concomitant Medications', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.CM.STUDYID', 'IT.CM.DOMAIN', 'IT.CM.USUBJID', 'IT.CM.CMSEQ', 'IT.CM.CMSPID', 'IT.CM.CMTRT', 'IT.CM.CMDECOD', 'IT.CM.CMINDC', 'IT.CM.CMCLAS', 'IT.CM.CMDOSE', 'IT.CM.CMDOSU', 'IT.CM.CMDOSFRQ', 'IT.CM.CMROUTE', 'IT.CM.VISITNUM', 'IT.CM.VISIT', 'IT.CM.VISITDY', 'IT.CM.CMDTC', 'IT.CM.CMSTDTC', 'IT.CM.CMENDTC', 'IT.CM.CMSTDY', 'IT.CM.CMENDY'], 'keySequence': ['IT.CM.STUDYID', 'IT.CM.USUBJID']}, {'OID': 'IG.SUPPDS', 'name': 'SUPPDS', 'description': 'Supplemental Qualifiers for DS', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.RDOMAIN', 'IT.SUPPDS.USUBJID', 'IT.SUPPDS.IDVAR', 'IT.SUPPDS.IDVARVAL', 'IT.SUPPDS.QNAM', 'IT.SUPPDS.QLABEL', 'IT.SUPPDS.QVAL', 'IT.SUPPDS.QORIG', 'IT.SUPPDS.QEVAL'], 'keySequence': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.USUBJID']}, {'OID': 'IG.EX', 'name': 'EX', 'description': 'Exposure', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.EX.STUDYID', 'IT.EX.DOMAIN', 'IT.EX.USUBJID', 'IT.EX.EXSEQ', 'IT.EX.EXTRT', 'IT.EX.EXDOSE', 'IT.EX.EXDOSU', 'IT.EX.EXDOSFRM', 'IT.EX.EXDOSFRQ', 'IT.EX.EXROUTE', 'IT.EX.VISITNUM', 'IT.EX.VISIT', 'IT.EX.VISITDY', 'IT.EX.EXSTDTC', 'IT.EX.EXENDTC', 'IT.EX.EXSTDY', 'IT.EX.EXENDY'], 'keySequence': ['IT.EX.STUDYID', 'IT.EX.USUBJID']}, {'OID': 'IG.VS', 'name': 'VS', 'description': 'Vital Signs', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.VS.STUDYID', 'IT.VS.DOMAIN', 'IT.VS.USUBJID', 'IT.VS.VSSEQ', 'IT.VS.VSTESTCD', 'IT.VS.VSTEST', 'IT.VS.VSPOS', 'IT.VS.VSORRES', 'IT.VS.VSORRESU', 'IT.VS.VSSTRESC', 'IT.VS.VSSTRESN', 'IT.VS.VSSTRESU', 'IT.VS.VSSTAT', 'IT.VS.VSLOC', 'IT.VS.VSBLFL', 'IT.VS.VISITNUM', 'IT.VS.VISIT', 'IT.VS.VISITDY', 'IT.VS.VSDTC', 'IT.VS.VSDY', 'IT.VS.VSTPT', 'IT.VS.VSTPTNUM', 'IT.VS.VSELTM', 'IT.VS.VSTPTREF'], 'keySequence': ['IT.VS.STUDYID', 'IT.VS.USUBJID']}, {'OID': 'IG.MH', 'name': 'MH', 'description': 'Medical History', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.MH.STUDYID', 'IT.MH.DOMAIN', 'IT.MH.USUBJID', 'IT.MH.MHSEQ', 'IT.MH.MHSPID', 'IT.MH.MHTERM', 'IT.MH.MHLLT', 'IT.MH.MHDECOD', 'IT.MH.MHHLT', 'IT.MH.MHHLGT', 'IT.MH.MHCAT', 'IT.MH.MHBODSYS', 'IT.MH.MHSEV', 'IT.MH.VISITNUM', 'IT.MH.VISIT', 'IT.MH.VISITDY', 'IT.MH.MHDTC', 'IT.MH.MHSTDTC', 'IT.MH.MHDY'], 'keySequence': ['IT.MH.STUDYID', 'IT.MH.USUBJID']}, {'OID': 'IG.DS', 'name': 'DS', 'description': 'Disposition', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DS.STUDYID', 'IT.DS.DOMAIN', 'IT.DS.USUBJID', 'IT.DS.DSSEQ', 'IT.DS.DSSPID', 'IT.DS.DSTERM', 'IT.DS.DSDECOD', 'IT.DS.DSCAT', 'IT.DS.VISITNUM', 'IT.DS.VISIT', 'IT.DS.DSDTC', 'IT.DS.DSSTDTC', 'IT.DS.DSSTDY'], 'keySequence': ['IT.DS.STUDYID', 'IT.DS.USUBJID']}], 'standards': [{'OID': 'STD.1', 'name': 'SDTMIG', 'type': 'IG', 'version': '3.4', 'status': 'Final'}, {'OID': 'STD.2', 'name': 'CDISC/NCI', 'type': 'CT', 'version': '2024-09-27', 'status': 'Final'}]} instance_index=0 instantiates='MetaDataVersion' context=["'IT.CM.STUDYID' is not of type 'object'", "'IT.CM.DOMAIN' is not of type 'object'", "'IT.CM.USUBJID' is not of type 'object'", "'IT.CM.CMSEQ' is not of type 'object'", "'IT.CM.CMSPID' is not of type 'object'", "'IT.CM.CMTRT' is not of type 'object'", "'IT.CM.CMDECOD' is not of type 'object'", "'IT.CM.CMINDC' is not of type 'object'", "'IT.CM.CMCLAS' is not of type 'object'", "'IT.CM.CMDOSE' is not of type 'object'", "'IT.CM.CMDOSU' is not of type 'object'", "'IT.CM.CMDOSFRQ' is not of type 'object'", "'IT.CM.CMROUTE' is not of type 'object'", "'IT.CM.VISITNUM' is not of type 'object'", "'IT.CM.VISIT' is not of type 'object'", "'IT.CM.VISITDY' is not of type 'object'", "'IT.CM.CMDTC' is not of type 'object'", "'IT.CM.CMSTDTC' is not of type 'object'", "'IT.CM.CMENDTC' is not of type 'object'", "'IT.CM.CMSTDY' is not of type 'object'", "'IT.CM.CMENDY' is not of type 'object'", "'IT.CM.STUDYID' is not of type 'object'", "'IT.CM.USUBJID' is not of type 'object'", "'IT.CM.STUDYID' is not of type 'object'", "'IT.CM.DOMAIN' is not of type 'object'", "'IT.CM.USUBJID' is not of type 'object'", "'IT.CM.CMSEQ' is not of type 'object'", "'IT.CM.CMSPID' is not of type 'object'", "'IT.CM.CMTRT' is not of type 'object'", "'IT.CM.CMDECOD' is not of type 'object'", "'IT.CM.CMINDC' is not of type 'object'", "'IT.CM.CMCLAS' is not of type 'object'", "'IT.CM.CMDOSE' is not of type 'object'", "'IT.CM.CMDOSU' is not of type 'object'", "'IT.CM.CMDOSFRQ' is not of type 'object'", "'IT.CM.CMROUTE' is not of type 'object'", "'IT.CM.VISITNUM' is not of type 'object'", "'IT.CM.VISIT' is not of type 'object'", "'IT.CM.VISITDY' is not of type 'object'", "'IT.CM.CMDTC' is not of type 'object'", "'IT.CM.CMSTDTC' is not of type 'object'", "'IT.CM.CMENDTC' is not of type 'object'", "'IT.CM.CMSTDY' is not of type 'object'", "'IT.CM.CMENDY' is not of type 'object'", "'IT.CM.STUDYID' is not of type 'object'", "'IT.CM.USUBJID' is not of type 'object'"] source=&lt;ValidationError: "{'OID': 'IG.CM', 'name': 'CM', 'description': 'Concomitant Medications', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.CM.STUDYID', 'IT.CM.DOMAIN', 'IT.CM.USUBJID', 'IT.CM.CMSEQ', 'IT.CM.CMSPID', 'IT.CM.CMTRT', 'IT.CM.CMDECOD', 'IT.CM.CMINDC', 'IT.CM.CMCLAS', 'IT.CM.CMDOSE', 'IT.CM.CMDOSU', 'IT.CM.CMDOSFRQ', 'IT.CM.CMROUTE', 'IT.CM.VISITNUM', 'IT.CM.VISIT', 'IT.CM.VISITDY', 'IT.CM.CMDTC', 'IT.CM.CMSTDTC', 'IT.CM.CMENDTC', 'IT.CM.CMSTDY', 'IT.CM.CMENDY'], 'keySequence': ['IT.CM.STUDYID', 'IT.CM.USUBJID']} is not valid under any of the given schemas"&gt;</t>
+          <t>'OID' is a required property in /items/175/origin/documents/0</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>type='jsonschema validation' severity=&lt;Severity.ERROR: 'ERROR'&gt; message="{'OID': 'IG.SUPPDS', 'name': 'SUPPDS', 'description': 'Supplemental Qualifiers for DS', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.RDOMAIN', 'IT.SUPPDS.USUBJID', 'IT.SUPPDS.IDVAR', 'IT.SUPPDS.IDVARVAL', 'IT.SUPPDS.QNAM', 'IT.SUPPDS.QLABEL', 'IT.SUPPDS.QVAL', 'IT.SUPPDS.QORIG', 'IT.SUPPDS.QEVAL'], 'keySequence': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.USUBJID']} is not valid under any of the given schemas in /itemGroups/6" instance={'OID': 'MDV.360i CDISC PILOT - LZZT', 'name': 'MDV 360i CDISC PILOT - LZZT', 'description': 'Data Definitions for 360i CDISC PILOT - LZZT', 'fileOID': 'ODM.DEFINE-360I.360i CDISC PILOT - LZZT', 'creationDateTime': '2026-04-15T20:36:55.421402+00:00', 'odmVersion': '1.3.2', 'fileType': 'Snapshot', 'originator': 'Define-360i Processor', 'context': 'Other', 'defineVersion': '2.1.0', 'studyOID': '', 'studyName': '360i CDISC PILOT - LZZT', 'studyDescription': "Safety and Efficacy of the Xanomeline Transdermal Therapeutic System (TTS) in Patients with Mild to Moderate Alzheimer's Disease", 'protocolName': '360i LZZT Xanomeline (LY246708)', 'itemGroups': [{'OID': 'IG.SC', 'name': 'SC', 'description': 'Subject Characteristics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SC.STUDYID', 'IT.SC.DOMAIN', 'IT.SC.USUBJID', 'IT.SC.SCSEQ', 'IT.SC.SCTESTCD', 'IT.SC.SCTEST', 'IT.SC.SCCAT', 'IT.SC.SCORRES', 'IT.SC.SCORRESU', 'IT.SC.SCSTRESC', 'IT.SC.SCSTRESN', 'IT.SC.SCSTRESU', 'IT.SC.SCDTC', 'IT.SC.SCDY'], 'keySequence': ['IT.SC.STUDYID', 'IT.SC.USUBJID']}, {'OID': 'IG.LB', 'name': 'LB', 'description': 'Laboratory Test Findings', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.LB.STUDYID', 'IT.LB.DOMAIN', 'IT.LB.USUBJID', 'IT.LB.LBSEQ', 'IT.LB.LBTESTCD', 'IT.LB.LBTEST', 'IT.LB.LBCAT', 'IT.LB.LBORRES', 'IT.LB.LBORRESU', 'IT.LB.LBORNRLO', 'IT.LB.LBORNRHI', 'IT.LB.LBSTRESC', 'IT.LB.LBSTRESN', 'IT.LB.LBSTRESU', 'IT.LB.LBSTNRLO', 'IT.LB.LBSTNRHI', 'IT.LB.LBNRIND', 'IT.LB.LBBLFL', 'IT.LB.VISITNUM', 'IT.LB.VISIT', 'IT.LB.VISITDY', 'IT.LB.LBDTC', 'IT.LB.LBDY'], 'keySequence': ['IT.LB.STUDYID', 'IT.LB.USUBJID']}, {'OID': 'IG.AE', 'name': 'AE', 'description': 'Adverse Events', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.AE.STUDYID', 'IT.AE.DOMAIN', 'IT.AE.USUBJID', 'IT.AE.AESEQ', 'IT.AE.AESPID', 'IT.AE.AETERM', 'IT.AE.AELLT', 'IT.AE.AELLTCD', 'IT.AE.AEDECOD', 'IT.AE.AEPTCD', 'IT.AE.AEHLT', 'IT.AE.AEHLTCD', 'IT.AE.AEHLGT', 'IT.AE.AEHLGTCD', 'IT.AE.AEBODSYS', 'IT.AE.AEBDSYCD', 'IT.AE.AESOC', 'IT.AE.AESOCCD', 'IT.AE.AESEV', 'IT.AE.AESER', 'IT.AE.AEACN', 'IT.AE.AEREL', 'IT.AE.AEOUT', 'IT.AE.AESCAN', 'IT.AE.AESCONG', 'IT.AE.AESDISAB', 'IT.AE.AESDTH', 'IT.AE.AESHOSP', 'IT.AE.AESLIFE', 'IT.AE.AESOD', 'IT.AE.AEDTC', 'IT.AE.AESTDTC', 'IT.AE.AEENDTC', 'IT.AE.AESTDY', 'IT.AE.AEENDY'], 'keySequence': ['IT.AE.STUDYID', 'IT.AE.USUBJID']}, {'OID': 'IG.QS', 'name': 'QS', 'description': 'Questionnaires', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.QS.STUDYID', 'IT.QS.DOMAIN', 'IT.QS.USUBJID', 'IT.QS.QSSEQ', 'IT.QS.QSTESTCD', 'IT.QS.QSTEST', 'IT.QS.QSCAT', 'IT.QS.QSSCAT', 'IT.QS.QSORRES', 'IT.QS.QSORRESU', 'IT.QS.QSSTRESC', 'IT.QS.QSSTRESN', 'IT.QS.QSSTRESU', 'IT.QS.QSBLFL', 'IT.QS.QSDRVFL', 'IT.QS.VISITNUM', 'IT.QS.VISIT', 'IT.QS.VISITDY', 'IT.QS.QSDTC', 'IT.QS.QSDY'], 'keySequence': ['IT.QS.STUDYID', 'IT.QS.USUBJID']}, {'OID': 'IG.DM', 'name': 'DM', 'description': 'Demographics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DM.STUDYID', 'IT.DM.SITEID', 'IT.DM.DOMAIN', 'IT.DM.USUBJID', 'IT.DM.SUBJID', 'IT.DM.RFSTDTC', 'IT.DM.RFENDTC', 'IT.DM.RFXSTDTC', 'IT.DM.RFXENDTC', 'IT.DM.RFICDTC', 'IT.DM.RFPENDTC', 'IT.DM.DTHDTC', 'IT.DM.DTHFL', 'IT.DM.AGE', 'IT.DM.AGEU', 'IT.DM.SEX', 'IT.DM.RACE', 'IT.DM.ETHNIC', 'IT.DM.COUNTRY', 'IT.DM.ARM', 'IT.DM.ARMCD', 'IT.DM.ACTARM', 'IT.DM.ACTARMCD', 'IT.DM.DMDTC', 'IT.DM.DMDY'], 'keySequence': ['IT.DM.STUDYID', 'IT.DM.USUBJID']}, {'OID': 'IG.CM', 'name': 'CM', 'description': 'Concomitant Medications', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.CM.STUDYID', 'IT.CM.DOMAIN', 'IT.CM.USUBJID', 'IT.CM.CMSEQ', 'IT.CM.CMSPID', 'IT.CM.CMTRT', 'IT.CM.CMDECOD', 'IT.CM.CMINDC', 'IT.CM.CMCLAS', 'IT.CM.CMDOSE', 'IT.CM.CMDOSU', 'IT.CM.CMDOSFRQ', 'IT.CM.CMROUTE', 'IT.CM.VISITNUM', 'IT.CM.VISIT', 'IT.CM.VISITDY', 'IT.CM.CMDTC', 'IT.CM.CMSTDTC', 'IT.CM.CMENDTC', 'IT.CM.CMSTDY', 'IT.CM.CMENDY'], 'keySequence': ['IT.CM.STUDYID', 'IT.CM.USUBJID']}, {'OID': 'IG.SUPPDS', 'name': 'SUPPDS', 'description': 'Supplemental Qualifiers for DS', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.RDOMAIN', 'IT.SUPPDS.USUBJID', 'IT.SUPPDS.IDVAR', 'IT.SUPPDS.IDVARVAL', 'IT.SUPPDS.QNAM', 'IT.SUPPDS.QLABEL', 'IT.SUPPDS.QVAL', 'IT.SUPPDS.QORIG', 'IT.SUPPDS.QEVAL'], 'keySequence': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.USUBJID']}, {'OID': 'IG.EX', 'name': 'EX', 'description': 'Exposure', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.EX.STUDYID', 'IT.EX.DOMAIN', 'IT.EX.USUBJID', 'IT.EX.EXSEQ', 'IT.EX.EXTRT', 'IT.EX.EXDOSE', 'IT.EX.EXDOSU', 'IT.EX.EXDOSFRM', 'IT.EX.EXDOSFRQ', 'IT.EX.EXROUTE', 'IT.EX.VISITNUM', 'IT.EX.VISIT', 'IT.EX.VISITDY', 'IT.EX.EXSTDTC', 'IT.EX.EXENDTC', 'IT.EX.EXSTDY', 'IT.EX.EXENDY'], 'keySequence': ['IT.EX.STUDYID', 'IT.EX.USUBJID']}, {'OID': 'IG.VS', 'name': 'VS', 'description': 'Vital Signs', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.VS.STUDYID', 'IT.VS.DOMAIN', 'IT.VS.USUBJID', 'IT.VS.VSSEQ', 'IT.VS.VSTESTCD', 'IT.VS.VSTEST', 'IT.VS.VSPOS', 'IT.VS.VSORRES', 'IT.VS.VSORRESU', 'IT.VS.VSSTRESC', 'IT.VS.VSSTRESN', 'IT.VS.VSSTRESU', 'IT.VS.VSSTAT', 'IT.VS.VSLOC', 'IT.VS.VSBLFL', 'IT.VS.VISITNUM', 'IT.VS.VISIT', 'IT.VS.VISITDY', 'IT.VS.VSDTC', 'IT.VS.VSDY', 'IT.VS.VSTPT', 'IT.VS.VSTPTNUM', 'IT.VS.VSELTM', 'IT.VS.VSTPTREF'], 'keySequence': ['IT.VS.STUDYID', 'IT.VS.USUBJID']}, {'OID': 'IG.MH', 'name': 'MH', 'description': 'Medical History', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.MH.STUDYID', 'IT.MH.DOMAIN', 'IT.MH.USUBJID', 'IT.MH.MHSEQ', 'IT.MH.MHSPID', 'IT.MH.MHTERM', 'IT.MH.MHLLT', 'IT.MH.MHDECOD', 'IT.MH.MHHLT', 'IT.MH.MHHLGT', 'IT.MH.MHCAT', 'IT.MH.MHBODSYS', 'IT.MH.MHSEV', 'IT.MH.VISITNUM', 'IT.MH.VISIT', 'IT.MH.VISITDY', 'IT.MH.MHDTC', 'IT.MH.MHSTDTC', 'IT.MH.MHDY'], 'keySequence': ['IT.MH.STUDYID', 'IT.MH.USUBJID']}, {'OID': 'IG.DS', 'name': 'DS', 'description': 'Disposition', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DS.STUDYID', 'IT.DS.DOMAIN', 'IT.DS.USUBJID', 'IT.DS.DSSEQ', 'IT.DS.DSSPID', 'IT.DS.DSTERM', 'IT.DS.DSDECOD', 'IT.DS.DSCAT', 'IT.DS.VISITNUM', 'IT.DS.VISIT', 'IT.DS.DSDTC', 'IT.DS.DSSTDTC', 'IT.DS.DSSTDY'], 'keySequence': ['IT.DS.STUDYID', 'IT.DS.USUBJID']}], 'standards': [{'OID': 'STD.1', 'name': 'SDTMIG', 'type': 'IG', 'version': '3.4', 'status': 'Final'}, {'OID': 'STD.2', 'name': 'CDISC/NCI', 'type': 'CT', 'version': '2024-09-27', 'status': 'Final'}]} instance_index=0 instantiates='MetaDataVersion' context=["'IT.SUPPDS.STUDYID' is not of type 'object'", "'IT.SUPPDS.RDOMAIN' is not of type 'object'", "'IT.SUPPDS.USUBJID' is not of type 'object'", "'IT.SUPPDS.IDVAR' is not of type 'object'", "'IT.SUPPDS.IDVARVAL' is not of type 'object'", "'IT.SUPPDS.QNAM' is not of type 'object'", "'IT.SUPPDS.QLABEL' is not of type 'object'", "'IT.SUPPDS.QVAL' is not of type 'object'", "'IT.SUPPDS.QORIG' is not of type 'object'", "'IT.SUPPDS.QEVAL' is not of type 'object'", "'IT.SUPPDS.STUDYID' is not of type 'object'", "'IT.SUPPDS.USUBJID' is not of type 'object'", "'IT.SUPPDS.STUDYID' is not of type 'object'", "'IT.SUPPDS.RDOMAIN' is not of type 'object'", "'IT.SUPPDS.USUBJID' is not of type 'object'", "'IT.SUPPDS.IDVAR' is not of type 'object'", "'IT.SUPPDS.IDVARVAL' is not of type 'object'", "'IT.SUPPDS.QNAM' is not of type 'object'", "'IT.SUPPDS.QLABEL' is not of type 'object'", "'IT.SUPPDS.QVAL' is not of type 'object'", "'IT.SUPPDS.QORIG' is not of type 'object'", "'IT.SUPPDS.QEVAL' is not of type 'object'", "'IT.SUPPDS.STUDYID' is not of type 'object'", "'IT.SUPPDS.USUBJID' is not of type 'object'"] source=&lt;ValidationError: "{'OID': 'IG.SUPPDS', 'name': 'SUPPDS', 'description': 'Supplemental Qualifiers for DS', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.RDOMAIN', 'IT.SUPPDS.USUBJID', 'IT.SUPPDS.IDVAR', 'IT.SUPPDS.IDVARVAL', 'IT.SUPPDS.QNAM', 'IT.SUPPDS.QLABEL', 'IT.SUPPDS.QVAL', 'IT.SUPPDS.QORIG', 'IT.SUPPDS.QEVAL'], 'keySequence': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.USUBJID']} is not valid under any of the given schemas"&gt;</t>
+          <t>'OID' is a required property in /items/176/origin/documents/0</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>type='jsonschema validation' severity=&lt;Severity.ERROR: 'ERROR'&gt; message="{'OID': 'IG.EX', 'name': 'EX', 'description': 'Exposure', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.EX.STUDYID', 'IT.EX.DOMAIN', 'IT.EX.USUBJID', 'IT.EX.EXSEQ', 'IT.EX.EXTRT', 'IT.EX.EXDOSE', 'IT.EX.EXDOSU', 'IT.EX.EXDOSFRM', 'IT.EX.EXDOSFRQ', 'IT.EX.EXROUTE', 'IT.EX.VISITNUM', 'IT.EX.VISIT', 'IT.EX.VISITDY', 'IT.EX.EXSTDTC', 'IT.EX.EXENDTC', 'IT.EX.EXSTDY', 'IT.EX.EXENDY'], 'keySequence': ['IT.EX.STUDYID', 'IT.EX.USUBJID']} is not valid under any of the given schemas in /itemGroups/7" instance={'OID': 'MDV.360i CDISC PILOT - LZZT', 'name': 'MDV 360i CDISC PILOT - LZZT', 'description': 'Data Definitions for 360i CDISC PILOT - LZZT', 'fileOID': 'ODM.DEFINE-360I.360i CDISC PILOT - LZZT', 'creationDateTime': '2026-04-15T20:36:55.421402+00:00', 'odmVersion': '1.3.2', 'fileType': 'Snapshot', 'originator': 'Define-360i Processor', 'context': 'Other', 'defineVersion': '2.1.0', 'studyOID': '', 'studyName': '360i CDISC PILOT - LZZT', 'studyDescription': "Safety and Efficacy of the Xanomeline Transdermal Therapeutic System (TTS) in Patients with Mild to Moderate Alzheimer's Disease", 'protocolName': '360i LZZT Xanomeline (LY246708)', 'itemGroups': [{'OID': 'IG.SC', 'name': 'SC', 'description': 'Subject Characteristics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SC.STUDYID', 'IT.SC.DOMAIN', 'IT.SC.USUBJID', 'IT.SC.SCSEQ', 'IT.SC.SCTESTCD', 'IT.SC.SCTEST', 'IT.SC.SCCAT', 'IT.SC.SCORRES', 'IT.SC.SCORRESU', 'IT.SC.SCSTRESC', 'IT.SC.SCSTRESN', 'IT.SC.SCSTRESU', 'IT.SC.SCDTC', 'IT.SC.SCDY'], 'keySequence': ['IT.SC.STUDYID', 'IT.SC.USUBJID']}, {'OID': 'IG.LB', 'name': 'LB', 'description': 'Laboratory Test Findings', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.LB.STUDYID', 'IT.LB.DOMAIN', 'IT.LB.USUBJID', 'IT.LB.LBSEQ', 'IT.LB.LBTESTCD', 'IT.LB.LBTEST', 'IT.LB.LBCAT', 'IT.LB.LBORRES', 'IT.LB.LBORRESU', 'IT.LB.LBORNRLO', 'IT.LB.LBORNRHI', 'IT.LB.LBSTRESC', 'IT.LB.LBSTRESN', 'IT.LB.LBSTRESU', 'IT.LB.LBSTNRLO', 'IT.LB.LBSTNRHI', 'IT.LB.LBNRIND', 'IT.LB.LBBLFL', 'IT.LB.VISITNUM', 'IT.LB.VISIT', 'IT.LB.VISITDY', 'IT.LB.LBDTC', 'IT.LB.LBDY'], 'keySequence': ['IT.LB.STUDYID', 'IT.LB.USUBJID']}, {'OID': 'IG.AE', 'name': 'AE', 'description': 'Adverse Events', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.AE.STUDYID', 'IT.AE.DOMAIN', 'IT.AE.USUBJID', 'IT.AE.AESEQ', 'IT.AE.AESPID', 'IT.AE.AETERM', 'IT.AE.AELLT', 'IT.AE.AELLTCD', 'IT.AE.AEDECOD', 'IT.AE.AEPTCD', 'IT.AE.AEHLT', 'IT.AE.AEHLTCD', 'IT.AE.AEHLGT', 'IT.AE.AEHLGTCD', 'IT.AE.AEBODSYS', 'IT.AE.AEBDSYCD', 'IT.AE.AESOC', 'IT.AE.AESOCCD', 'IT.AE.AESEV', 'IT.AE.AESER', 'IT.AE.AEACN', 'IT.AE.AEREL', 'IT.AE.AEOUT', 'IT.AE.AESCAN', 'IT.AE.AESCONG', 'IT.AE.AESDISAB', 'IT.AE.AESDTH', 'IT.AE.AESHOSP', 'IT.AE.AESLIFE', 'IT.AE.AESOD', 'IT.AE.AEDTC', 'IT.AE.AESTDTC', 'IT.AE.AEENDTC', 'IT.AE.AESTDY', 'IT.AE.AEENDY'], 'keySequence': ['IT.AE.STUDYID', 'IT.AE.USUBJID']}, {'OID': 'IG.QS', 'name': 'QS', 'description': 'Questionnaires', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.QS.STUDYID', 'IT.QS.DOMAIN', 'IT.QS.USUBJID', 'IT.QS.QSSEQ', 'IT.QS.QSTESTCD', 'IT.QS.QSTEST', 'IT.QS.QSCAT', 'IT.QS.QSSCAT', 'IT.QS.QSORRES', 'IT.QS.QSORRESU', 'IT.QS.QSSTRESC', 'IT.QS.QSSTRESN', 'IT.QS.QSSTRESU', 'IT.QS.QSBLFL', 'IT.QS.QSDRVFL', 'IT.QS.VISITNUM', 'IT.QS.VISIT', 'IT.QS.VISITDY', 'IT.QS.QSDTC', 'IT.QS.QSDY'], 'keySequence': ['IT.QS.STUDYID', 'IT.QS.USUBJID']}, {'OID': 'IG.DM', 'name': 'DM', 'description': 'Demographics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DM.STUDYID', 'IT.DM.SITEID', 'IT.DM.DOMAIN', 'IT.DM.USUBJID', 'IT.DM.SUBJID', 'IT.DM.RFSTDTC', 'IT.DM.RFENDTC', 'IT.DM.RFXSTDTC', 'IT.DM.RFXENDTC', 'IT.DM.RFICDTC', 'IT.DM.RFPENDTC', 'IT.DM.DTHDTC', 'IT.DM.DTHFL', 'IT.DM.AGE', 'IT.DM.AGEU', 'IT.DM.SEX', 'IT.DM.RACE', 'IT.DM.ETHNIC', 'IT.DM.COUNTRY', 'IT.DM.ARM', 'IT.DM.ARMCD', 'IT.DM.ACTARM', 'IT.DM.ACTARMCD', 'IT.DM.DMDTC', 'IT.DM.DMDY'], 'keySequence': ['IT.DM.STUDYID', 'IT.DM.USUBJID']}, {'OID': 'IG.CM', 'name': 'CM', 'description': 'Concomitant Medications', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.CM.STUDYID', 'IT.CM.DOMAIN', 'IT.CM.USUBJID', 'IT.CM.CMSEQ', 'IT.CM.CMSPID', 'IT.CM.CMTRT', 'IT.CM.CMDECOD', 'IT.CM.CMINDC', 'IT.CM.CMCLAS', 'IT.CM.CMDOSE', 'IT.CM.CMDOSU', 'IT.CM.CMDOSFRQ', 'IT.CM.CMROUTE', 'IT.CM.VISITNUM', 'IT.CM.VISIT', 'IT.CM.VISITDY', 'IT.CM.CMDTC', 'IT.CM.CMSTDTC', 'IT.CM.CMENDTC', 'IT.CM.CMSTDY', 'IT.CM.CMENDY'], 'keySequence': ['IT.CM.STUDYID', 'IT.CM.USUBJID']}, {'OID': 'IG.SUPPDS', 'name': 'SUPPDS', 'description': 'Supplemental Qualifiers for DS', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.RDOMAIN', 'IT.SUPPDS.USUBJID', 'IT.SUPPDS.IDVAR', 'IT.SUPPDS.IDVARVAL', 'IT.SUPPDS.QNAM', 'IT.SUPPDS.QLABEL', 'IT.SUPPDS.QVAL', 'IT.SUPPDS.QORIG', 'IT.SUPPDS.QEVAL'], 'keySequence': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.USUBJID']}, {'OID': 'IG.EX', 'name': 'EX', 'description': 'Exposure', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.EX.STUDYID', 'IT.EX.DOMAIN', 'IT.EX.USUBJID', 'IT.EX.EXSEQ', 'IT.EX.EXTRT', 'IT.EX.EXDOSE', 'IT.EX.EXDOSU', 'IT.EX.EXDOSFRM', 'IT.EX.EXDOSFRQ', 'IT.EX.EXROUTE', 'IT.EX.VISITNUM', 'IT.EX.VISIT', 'IT.EX.VISITDY', 'IT.EX.EXSTDTC', 'IT.EX.EXENDTC', 'IT.EX.EXSTDY', 'IT.EX.EXENDY'], 'keySequence': ['IT.EX.STUDYID', 'IT.EX.USUBJID']}, {'OID': 'IG.VS', 'name': 'VS', 'description': 'Vital Signs', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.VS.STUDYID', 'IT.VS.DOMAIN', 'IT.VS.USUBJID', 'IT.VS.VSSEQ', 'IT.VS.VSTESTCD', 'IT.VS.VSTEST', 'IT.VS.VSPOS', 'IT.VS.VSORRES', 'IT.VS.VSORRESU', 'IT.VS.VSSTRESC', 'IT.VS.VSSTRESN', 'IT.VS.VSSTRESU', 'IT.VS.VSSTAT', 'IT.VS.VSLOC', 'IT.VS.VSBLFL', 'IT.VS.VISITNUM', 'IT.VS.VISIT', 'IT.VS.VISITDY', 'IT.VS.VSDTC', 'IT.VS.VSDY', 'IT.VS.VSTPT', 'IT.VS.VSTPTNUM', 'IT.VS.VSELTM', 'IT.VS.VSTPTREF'], 'keySequence': ['IT.VS.STUDYID', 'IT.VS.USUBJID']}, {'OID': 'IG.MH', 'name': 'MH', 'description': 'Medical History', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.MH.STUDYID', 'IT.MH.DOMAIN', 'IT.MH.USUBJID', 'IT.MH.MHSEQ', 'IT.MH.MHSPID', 'IT.MH.MHTERM', 'IT.MH.MHLLT', 'IT.MH.MHDECOD', 'IT.MH.MHHLT', 'IT.MH.MHHLGT', 'IT.MH.MHCAT', 'IT.MH.MHBODSYS', 'IT.MH.MHSEV', 'IT.MH.VISITNUM', 'IT.MH.VISIT', 'IT.MH.VISITDY', 'IT.MH.MHDTC', 'IT.MH.MHSTDTC', 'IT.MH.MHDY'], 'keySequence': ['IT.MH.STUDYID', 'IT.MH.USUBJID']}, {'OID': 'IG.DS', 'name': 'DS', 'description': 'Disposition', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DS.STUDYID', 'IT.DS.DOMAIN', 'IT.DS.USUBJID', 'IT.DS.DSSEQ', 'IT.DS.DSSPID', 'IT.DS.DSTERM', 'IT.DS.DSDECOD', 'IT.DS.DSCAT', 'IT.DS.VISITNUM', 'IT.DS.VISIT', 'IT.DS.DSDTC', 'IT.DS.DSSTDTC', 'IT.DS.DSSTDY'], 'keySequence': ['IT.DS.STUDYID', 'IT.DS.USUBJID']}], 'standards': [{'OID': 'STD.1', 'name': 'SDTMIG', 'type': 'IG', 'version': '3.4', 'status': 'Final'}, {'OID': 'STD.2', 'name': 'CDISC/NCI', 'type': 'CT', 'version': '2024-09-27', 'status': 'Final'}]} instance_index=0 instantiates='MetaDataVersion' context=["'IT.EX.STUDYID' is not of type 'object'", "'IT.EX.DOMAIN' is not of type 'object'", "'IT.EX.USUBJID' is not of type 'object'", "'IT.EX.EXSEQ' is not of type 'object'", "'IT.EX.EXTRT' is not of type 'object'", "'IT.EX.EXDOSE' is not of type 'object'", "'IT.EX.EXDOSU' is not of type 'object'", "'IT.EX.EXDOSFRM' is not of type 'object'", "'IT.EX.EXDOSFRQ' is not of type 'object'", "'IT.EX.EXROUTE' is not of type 'object'", "'IT.EX.VISITNUM' is not of type 'object'", "'IT.EX.VISIT' is not of type 'object'", "'IT.EX.VISITDY' is not of type 'object'", "'IT.EX.EXSTDTC' is not of type 'object'", "'IT.EX.EXENDTC' is not of type 'object'", "'IT.EX.EXSTDY' is not of type 'object'", "'IT.EX.EXENDY' is not of type 'object'", "'IT.EX.STUDYID' is not of type 'object'", "'IT.EX.USUBJID' is not of type 'object'", "'IT.EX.STUDYID' is not of type 'object'", "'IT.EX.DOMAIN' is not of type 'object'", "'IT.EX.USUBJID' is not of type 'object'", "'IT.EX.EXSEQ' is not of type 'object'", "'IT.EX.EXTRT' is not of type 'object'", "'IT.EX.EXDOSE' is not of type 'object'", "'IT.EX.EXDOSU' is not of type 'object'", "'IT.EX.EXDOSFRM' is not of type 'object'", "'IT.EX.EXDOSFRQ' is not of type 'object'", "'IT.EX.EXROUTE' is not of type 'object'", "'IT.EX.VISITNUM' is not of type 'object'", "'IT.EX.VISIT' is not of type 'object'", "'IT.EX.VISITDY' is not of type 'object'", "'IT.EX.EXSTDTC' is not of type 'object'", "'IT.EX.EXENDTC' is not of type 'object'", "'IT.EX.EXSTDY' is not of type 'object'", "'IT.EX.EXENDY' is not of type 'object'", "'IT.EX.STUDYID' is not of type 'object'", "'IT.EX.USUBJID' is not of type 'object'"] source=&lt;ValidationError: "{'OID': 'IG.EX', 'name': 'EX', 'description': 'Exposure', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.EX.STUDYID', 'IT.EX.DOMAIN', 'IT.EX.USUBJID', 'IT.EX.EXSEQ', 'IT.EX.EXTRT', 'IT.EX.EXDOSE', 'IT.EX.EXDOSU', 'IT.EX.EXDOSFRM', 'IT.EX.EXDOSFRQ', 'IT.EX.EXROUTE', 'IT.EX.VISITNUM', 'IT.EX.VISIT', 'IT.EX.VISITDY', 'IT.EX.EXSTDTC', 'IT.EX.EXENDTC', 'IT.EX.EXSTDY', 'IT.EX.EXENDY'], 'keySequence': ['IT.EX.STUDYID', 'IT.EX.USUBJID']} is not valid under any of the given schemas"&gt;</t>
+          <t>'OID' is a required property in /items/177/origin/documents/0</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>type='jsonschema validation' severity=&lt;Severity.ERROR: 'ERROR'&gt; message="{'OID': 'IG.VS', 'name': 'VS', 'description': 'Vital Signs', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.VS.STUDYID', 'IT.VS.DOMAIN', 'IT.VS.USUBJID', 'IT.VS.VSSEQ', 'IT.VS.VSTESTCD', 'IT.VS.VSTEST', 'IT.VS.VSPOS', 'IT.VS.VSORRES', 'IT.VS.VSORRESU', 'IT.VS.VSSTRESC', 'IT.VS.VSSTRESN', 'IT.VS.VSSTRESU', 'IT.VS.VSSTAT', 'IT.VS.VSLOC', 'IT.VS.VSBLFL', 'IT.VS.VISITNUM', 'IT.VS.VISIT', 'IT.VS.VISITDY', 'IT.VS.VSDTC', 'IT.VS.VSDY', 'IT.VS.VSTPT', 'IT.VS.VSTPTNUM', 'IT.VS.VSELTM', 'IT.VS.VSTPTREF'], 'keySequence': ['IT.VS.STUDYID', 'IT.VS.USUBJID']} is not valid under any of the given schemas in /itemGroups/8" instance={'OID': 'MDV.360i CDISC PILOT - LZZT', 'name': 'MDV 360i CDISC PILOT - LZZT', 'description': 'Data Definitions for 360i CDISC PILOT - LZZT', 'fileOID': 'ODM.DEFINE-360I.360i CDISC PILOT - LZZT', 'creationDateTime': '2026-04-15T20:36:55.421402+00:00', 'odmVersion': '1.3.2', 'fileType': 'Snapshot', 'originator': 'Define-360i Processor', 'context': 'Other', 'defineVersion': '2.1.0', 'studyOID': '', 'studyName': '360i CDISC PILOT - LZZT', 'studyDescription': "Safety and Efficacy of the Xanomeline Transdermal Therapeutic System (TTS) in Patients with Mild to Moderate Alzheimer's Disease", 'protocolName': '360i LZZT Xanomeline (LY246708)', 'itemGroups': [{'OID': 'IG.SC', 'name': 'SC', 'description': 'Subject Characteristics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SC.STUDYID', 'IT.SC.DOMAIN', 'IT.SC.USUBJID', 'IT.SC.SCSEQ', 'IT.SC.SCTESTCD', 'IT.SC.SCTEST', 'IT.SC.SCCAT', 'IT.SC.SCORRES', 'IT.SC.SCORRESU', 'IT.SC.SCSTRESC', 'IT.SC.SCSTRESN', 'IT.SC.SCSTRESU', 'IT.SC.SCDTC', 'IT.SC.SCDY'], 'keySequence': ['IT.SC.STUDYID', 'IT.SC.USUBJID']}, {'OID': 'IG.LB', 'name': 'LB', 'description': 'Laboratory Test Findings', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.LB.STUDYID', 'IT.LB.DOMAIN', 'IT.LB.USUBJID', 'IT.LB.LBSEQ', 'IT.LB.LBTESTCD', 'IT.LB.LBTEST', 'IT.LB.LBCAT', 'IT.LB.LBORRES', 'IT.LB.LBORRESU', 'IT.LB.LBORNRLO', 'IT.LB.LBORNRHI', 'IT.LB.LBSTRESC', 'IT.LB.LBSTRESN', 'IT.LB.LBSTRESU', 'IT.LB.LBSTNRLO', 'IT.LB.LBSTNRHI', 'IT.LB.LBNRIND', 'IT.LB.LBBLFL', 'IT.LB.VISITNUM', 'IT.LB.VISIT', 'IT.LB.VISITDY', 'IT.LB.LBDTC', 'IT.LB.LBDY'], 'keySequence': ['IT.LB.STUDYID', 'IT.LB.USUBJID']}, {'OID': 'IG.AE', 'name': 'AE', 'description': 'Adverse Events', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.AE.STUDYID', 'IT.AE.DOMAIN', 'IT.AE.USUBJID', 'IT.AE.AESEQ', 'IT.AE.AESPID', 'IT.AE.AETERM', 'IT.AE.AELLT', 'IT.AE.AELLTCD', 'IT.AE.AEDECOD', 'IT.AE.AEPTCD', 'IT.AE.AEHLT', 'IT.AE.AEHLTCD', 'IT.AE.AEHLGT', 'IT.AE.AEHLGTCD', 'IT.AE.AEBODSYS', 'IT.AE.AEBDSYCD', 'IT.AE.AESOC', 'IT.AE.AESOCCD', 'IT.AE.AESEV', 'IT.AE.AESER', 'IT.AE.AEACN', 'IT.AE.AEREL', 'IT.AE.AEOUT', 'IT.AE.AESCAN', 'IT.AE.AESCONG', 'IT.AE.AESDISAB', 'IT.AE.AESDTH', 'IT.AE.AESHOSP', 'IT.AE.AESLIFE', 'IT.AE.AESOD', 'IT.AE.AEDTC', 'IT.AE.AESTDTC', 'IT.AE.AEENDTC', 'IT.AE.AESTDY', 'IT.AE.AEENDY'], 'keySequence': ['IT.AE.STUDYID', 'IT.AE.USUBJID']}, {'OID': 'IG.QS', 'name': 'QS', 'description': 'Questionnaires', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.QS.STUDYID', 'IT.QS.DOMAIN', 'IT.QS.USUBJID', 'IT.QS.QSSEQ', 'IT.QS.QSTESTCD', 'IT.QS.QSTEST', 'IT.QS.QSCAT', 'IT.QS.QSSCAT', 'IT.QS.QSORRES', 'IT.QS.QSORRESU', 'IT.QS.QSSTRESC', 'IT.QS.QSSTRESN', 'IT.QS.QSSTRESU', 'IT.QS.QSBLFL', 'IT.QS.QSDRVFL', 'IT.QS.VISITNUM', 'IT.QS.VISIT', 'IT.QS.VISITDY', 'IT.QS.QSDTC', 'IT.QS.QSDY'], 'keySequence': ['IT.QS.STUDYID', 'IT.QS.USUBJID']}, {'OID': 'IG.DM', 'name': 'DM', 'description': 'Demographics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DM.STUDYID', 'IT.DM.SITEID', 'IT.DM.DOMAIN', 'IT.DM.USUBJID', 'IT.DM.SUBJID', 'IT.DM.RFSTDTC', 'IT.DM.RFENDTC', 'IT.DM.RFXSTDTC', 'IT.DM.RFXENDTC', 'IT.DM.RFICDTC', 'IT.DM.RFPENDTC', 'IT.DM.DTHDTC', 'IT.DM.DTHFL', 'IT.DM.AGE', 'IT.DM.AGEU', 'IT.DM.SEX', 'IT.DM.RACE', 'IT.DM.ETHNIC', 'IT.DM.COUNTRY', 'IT.DM.ARM', 'IT.DM.ARMCD', 'IT.DM.ACTARM', 'IT.DM.ACTARMCD', 'IT.DM.DMDTC', 'IT.DM.DMDY'], 'keySequence': ['IT.DM.STUDYID', 'IT.DM.USUBJID']}, {'OID': 'IG.CM', 'name': 'CM', 'description': 'Concomitant Medications', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.CM.STUDYID', 'IT.CM.DOMAIN', 'IT.CM.USUBJID', 'IT.CM.CMSEQ', 'IT.CM.CMSPID', 'IT.CM.CMTRT', 'IT.CM.CMDECOD', 'IT.CM.CMINDC', 'IT.CM.CMCLAS', 'IT.CM.CMDOSE', 'IT.CM.CMDOSU', 'IT.CM.CMDOSFRQ', 'IT.CM.CMROUTE', 'IT.CM.VISITNUM', 'IT.CM.VISIT', 'IT.CM.VISITDY', 'IT.CM.CMDTC', 'IT.CM.CMSTDTC', 'IT.CM.CMENDTC', 'IT.CM.CMSTDY', 'IT.CM.CMENDY'], 'keySequence': ['IT.CM.STUDYID', 'IT.CM.USUBJID']}, {'OID': 'IG.SUPPDS', 'name': 'SUPPDS', 'description': 'Supplemental Qualifiers for DS', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.RDOMAIN', 'IT.SUPPDS.USUBJID', 'IT.SUPPDS.IDVAR', 'IT.SUPPDS.IDVARVAL', 'IT.SUPPDS.QNAM', 'IT.SUPPDS.QLABEL', 'IT.SUPPDS.QVAL', 'IT.SUPPDS.QORIG', 'IT.SUPPDS.QEVAL'], 'keySequence': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.USUBJID']}, {'OID': 'IG.EX', 'name': 'EX', 'description': 'Exposure', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.EX.STUDYID', 'IT.EX.DOMAIN', 'IT.EX.USUBJID', 'IT.EX.EXSEQ', 'IT.EX.EXTRT', 'IT.EX.EXDOSE', 'IT.EX.EXDOSU', 'IT.EX.EXDOSFRM', 'IT.EX.EXDOSFRQ', 'IT.EX.EXROUTE', 'IT.EX.VISITNUM', 'IT.EX.VISIT', 'IT.EX.VISITDY', 'IT.EX.EXSTDTC', 'IT.EX.EXENDTC', 'IT.EX.EXSTDY', 'IT.EX.EXENDY'], 'keySequence': ['IT.EX.STUDYID', 'IT.EX.USUBJID']}, {'OID': 'IG.VS', 'name': 'VS', 'description': 'Vital Signs', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.VS.STUDYID', 'IT.VS.DOMAIN', 'IT.VS.USUBJID', 'IT.VS.VSSEQ', 'IT.VS.VSTESTCD', 'IT.VS.VSTEST', 'IT.VS.VSPOS', 'IT.VS.VSORRES', 'IT.VS.VSORRESU', 'IT.VS.VSSTRESC', 'IT.VS.VSSTRESN', 'IT.VS.VSSTRESU', 'IT.VS.VSSTAT', 'IT.VS.VSLOC', 'IT.VS.VSBLFL', 'IT.VS.VISITNUM', 'IT.VS.VISIT', 'IT.VS.VISITDY', 'IT.VS.VSDTC', 'IT.VS.VSDY', 'IT.VS.VSTPT', 'IT.VS.VSTPTNUM', 'IT.VS.VSELTM', 'IT.VS.VSTPTREF'], 'keySequence': ['IT.VS.STUDYID', 'IT.VS.USUBJID']}, {'OID': 'IG.MH', 'name': 'MH', 'description': 'Medical History', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.MH.STUDYID', 'IT.MH.DOMAIN', 'IT.MH.USUBJID', 'IT.MH.MHSEQ', 'IT.MH.MHSPID', 'IT.MH.MHTERM', 'IT.MH.MHLLT', 'IT.MH.MHDECOD', 'IT.MH.MHHLT', 'IT.MH.MHHLGT', 'IT.MH.MHCAT', 'IT.MH.MHBODSYS', 'IT.MH.MHSEV', 'IT.MH.VISITNUM', 'IT.MH.VISIT', 'IT.MH.VISITDY', 'IT.MH.MHDTC', 'IT.MH.MHSTDTC', 'IT.MH.MHDY'], 'keySequence': ['IT.MH.STUDYID', 'IT.MH.USUBJID']}, {'OID': 'IG.DS', 'name': 'DS', 'description': 'Disposition', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DS.STUDYID', 'IT.DS.DOMAIN', 'IT.DS.USUBJID', 'IT.DS.DSSEQ', 'IT.DS.DSSPID', 'IT.DS.DSTERM', 'IT.DS.DSDECOD', 'IT.DS.DSCAT', 'IT.DS.VISITNUM', 'IT.DS.VISIT', 'IT.DS.DSDTC', 'IT.DS.DSSTDTC', 'IT.DS.DSSTDY'], 'keySequence': ['IT.DS.STUDYID', 'IT.DS.USUBJID']}], 'standards': [{'OID': 'STD.1', 'name': 'SDTMIG', 'type': 'IG', 'version': '3.4', 'status': 'Final'}, {'OID': 'STD.2', 'name': 'CDISC/NCI', 'type': 'CT', 'version': '2024-09-27', 'status': 'Final'}]} instance_index=0 instantiates='MetaDataVersion' context=["'IT.VS.STUDYID' is not of type 'object'", "'IT.VS.DOMAIN' is not of type 'object'", "'IT.VS.USUBJID' is not of type 'object'", "'IT.VS.VSSEQ' is not of type 'object'", "'IT.VS.VSTESTCD' is not of type 'object'", "'IT.VS.VSTEST' is not of type 'object'", "'IT.VS.VSPOS' is not of type 'object'", "'IT.VS.VSORRES' is not of type 'object'", "'IT.VS.VSORRESU' is not of type 'object'", "'IT.VS.VSSTRESC' is not of type 'object'", "'IT.VS.VSSTRESN' is not of type 'object'", "'IT.VS.VSSTRESU' is not of type 'object'", "'IT.VS.VSSTAT' is not of type 'object'", "'IT.VS.VSLOC' is not of type 'object'", "'IT.VS.VSBLFL' is not of type 'object'", "'IT.VS.VISITNUM' is not of type 'object'", "'IT.VS.VISIT' is not of type 'object'", "'IT.VS.VISITDY' is not of type 'object'", "'IT.VS.VSDTC' is not of type 'object'", "'IT.VS.VSDY' is not of type 'object'", "'IT.VS.VSTPT' is not of type 'object'", "'IT.VS.VSTPTNUM' is not of type 'object'", "'IT.VS.VSELTM' is not of type 'object'", "'IT.VS.VSTPTREF' is not of type 'object'", "'IT.VS.STUDYID' is not of type 'object'", "'IT.VS.USUBJID' is not of type 'object'", "'IT.VS.STUDYID' is not of type 'object'", "'IT.VS.DOMAIN' is not of type 'object'", "'IT.VS.USUBJID' is not of type 'object'", "'IT.VS.VSSEQ' is not of type 'object'", "'IT.VS.VSTESTCD' is not of type 'object'", "'IT.VS.VSTEST' is not of type 'object'", "'IT.VS.VSPOS' is not of type 'object'", "'IT.VS.VSORRES' is not of type 'object'", "'IT.VS.VSORRESU' is not of type 'object'", "'IT.VS.VSSTRESC' is not of type 'object'", "'IT.VS.VSSTRESN' is not of type 'object'", "'IT.VS.VSSTRESU' is not of type 'object'", "'IT.VS.VSSTAT' is not of type 'object'", "'IT.VS.VSLOC' is not of type 'object'", "'IT.VS.VSBLFL' is not of type 'object'", "'IT.VS.VISITNUM' is not of type 'object'", "'IT.VS.VISIT' is not of type 'object'", "'IT.VS.VISITDY' is not of type 'object'", "'IT.VS.VSDTC' is not of type 'object'", "'IT.VS.VSDY' is not of type 'object'", "'IT.VS.VSTPT' is not of type 'object'", "'IT.VS.VSTPTNUM' is not of type 'object'", "'IT.VS.VSELTM' is not of type 'object'", "'IT.VS.VSTPTREF' is not of type 'object'", "'IT.VS.STUDYID' is not of type 'object'", "'IT.VS.USUBJID' is not of type 'object'"] source=&lt;ValidationError: "{'OID': 'IG.VS', 'name': 'VS', 'description': 'Vital Signs', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.VS.STUDYID', 'IT.VS.DOMAIN', 'IT.VS.USUBJID', 'IT.VS.VSSEQ', 'IT.VS.VSTESTCD', 'IT.VS.VSTEST', 'IT.VS.VSPOS', 'IT.VS.VSORRES', 'IT.VS.VSORRESU', 'IT.VS.VSSTRESC', 'IT.VS.VSSTRESN', 'IT.VS.VSSTRESU', 'IT.VS.VSSTAT', 'IT.VS.VSLOC', 'IT.VS.VSBLFL', 'IT.VS.VISITNUM', 'IT.VS.VISIT', 'IT.VS.VISITDY', 'IT.VS.VSDTC', 'IT.VS.VSDY', 'IT.VS.VSTPT', 'IT.VS.VSTPTNUM', 'IT.VS.VSELTM', 'IT.VS.VSTPTREF'], 'keySequence': ['IT.VS.STUDYID', 'IT.VS.USUBJID']} is not valid under any of the given schemas"&gt;</t>
+          <t>'OID' is a required property in /items/179/origin/documents/0</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>type='jsonschema validation' severity=&lt;Severity.ERROR: 'ERROR'&gt; message="{'OID': 'IG.MH', 'name': 'MH', 'description': 'Medical History', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.MH.STUDYID', 'IT.MH.DOMAIN', 'IT.MH.USUBJID', 'IT.MH.MHSEQ', 'IT.MH.MHSPID', 'IT.MH.MHTERM', 'IT.MH.MHLLT', 'IT.MH.MHDECOD', 'IT.MH.MHHLT', 'IT.MH.MHHLGT', 'IT.MH.MHCAT', 'IT.MH.MHBODSYS', 'IT.MH.MHSEV', 'IT.MH.VISITNUM', 'IT.MH.VISIT', 'IT.MH.VISITDY', 'IT.MH.MHDTC', 'IT.MH.MHSTDTC', 'IT.MH.MHDY'], 'keySequence': ['IT.MH.STUDYID', 'IT.MH.USUBJID']} is not valid under any of the given schemas in /itemGroups/9" instance={'OID': 'MDV.360i CDISC PILOT - LZZT', 'name': 'MDV 360i CDISC PILOT - LZZT', 'description': 'Data Definitions for 360i CDISC PILOT - LZZT', 'fileOID': 'ODM.DEFINE-360I.360i CDISC PILOT - LZZT', 'creationDateTime': '2026-04-15T20:36:55.421402+00:00', 'odmVersion': '1.3.2', 'fileType': 'Snapshot', 'originator': 'Define-360i Processor', 'context': 'Other', 'defineVersion': '2.1.0', 'studyOID': '', 'studyName': '360i CDISC PILOT - LZZT', 'studyDescription': "Safety and Efficacy of the Xanomeline Transdermal Therapeutic System (TTS) in Patients with Mild to Moderate Alzheimer's Disease", 'protocolName': '360i LZZT Xanomeline (LY246708)', 'itemGroups': [{'OID': 'IG.SC', 'name': 'SC', 'description': 'Subject Characteristics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SC.STUDYID', 'IT.SC.DOMAIN', 'IT.SC.USUBJID', 'IT.SC.SCSEQ', 'IT.SC.SCTESTCD', 'IT.SC.SCTEST', 'IT.SC.SCCAT', 'IT.SC.SCORRES', 'IT.SC.SCORRESU', 'IT.SC.SCSTRESC', 'IT.SC.SCSTRESN', 'IT.SC.SCSTRESU', 'IT.SC.SCDTC', 'IT.SC.SCDY'], 'keySequence': ['IT.SC.STUDYID', 'IT.SC.USUBJID']}, {'OID': 'IG.LB', 'name': 'LB', 'description': 'Laboratory Test Findings', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.LB.STUDYID', 'IT.LB.DOMAIN', 'IT.LB.USUBJID', 'IT.LB.LBSEQ', 'IT.LB.LBTESTCD', 'IT.LB.LBTEST', 'IT.LB.LBCAT', 'IT.LB.LBORRES', 'IT.LB.LBORRESU', 'IT.LB.LBORNRLO', 'IT.LB.LBORNRHI', 'IT.LB.LBSTRESC', 'IT.LB.LBSTRESN', 'IT.LB.LBSTRESU', 'IT.LB.LBSTNRLO', 'IT.LB.LBSTNRHI', 'IT.LB.LBNRIND', 'IT.LB.LBBLFL', 'IT.LB.VISITNUM', 'IT.LB.VISIT', 'IT.LB.VISITDY', 'IT.LB.LBDTC', 'IT.LB.LBDY'], 'keySequence': ['IT.LB.STUDYID', 'IT.LB.USUBJID']}, {'OID': 'IG.AE', 'name': 'AE', 'description': 'Adverse Events', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.AE.STUDYID', 'IT.AE.DOMAIN', 'IT.AE.USUBJID', 'IT.AE.AESEQ', 'IT.AE.AESPID', 'IT.AE.AETERM', 'IT.AE.AELLT', 'IT.AE.AELLTCD', 'IT.AE.AEDECOD', 'IT.AE.AEPTCD', 'IT.AE.AEHLT', 'IT.AE.AEHLTCD', 'IT.AE.AEHLGT', 'IT.AE.AEHLGTCD', 'IT.AE.AEBODSYS', 'IT.AE.AEBDSYCD', 'IT.AE.AESOC', 'IT.AE.AESOCCD', 'IT.AE.AESEV', 'IT.AE.AESER', 'IT.AE.AEACN', 'IT.AE.AEREL', 'IT.AE.AEOUT', 'IT.AE.AESCAN', 'IT.AE.AESCONG', 'IT.AE.AESDISAB', 'IT.AE.AESDTH', 'IT.AE.AESHOSP', 'IT.AE.AESLIFE', 'IT.AE.AESOD', 'IT.AE.AEDTC', 'IT.AE.AESTDTC', 'IT.AE.AEENDTC', 'IT.AE.AESTDY', 'IT.AE.AEENDY'], 'keySequence': ['IT.AE.STUDYID', 'IT.AE.USUBJID']}, {'OID': 'IG.QS', 'name': 'QS', 'description': 'Questionnaires', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.QS.STUDYID', 'IT.QS.DOMAIN', 'IT.QS.USUBJID', 'IT.QS.QSSEQ', 'IT.QS.QSTESTCD', 'IT.QS.QSTEST', 'IT.QS.QSCAT', 'IT.QS.QSSCAT', 'IT.QS.QSORRES', 'IT.QS.QSORRESU', 'IT.QS.QSSTRESC', 'IT.QS.QSSTRESN', 'IT.QS.QSSTRESU', 'IT.QS.QSBLFL', 'IT.QS.QSDRVFL', 'IT.QS.VISITNUM', 'IT.QS.VISIT', 'IT.QS.VISITDY', 'IT.QS.QSDTC', 'IT.QS.QSDY'], 'keySequence': ['IT.QS.STUDYID', 'IT.QS.USUBJID']}, {'OID': 'IG.DM', 'name': 'DM', 'description': 'Demographics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DM.STUDYID', 'IT.DM.SITEID', 'IT.DM.DOMAIN', 'IT.DM.USUBJID', 'IT.DM.SUBJID', 'IT.DM.RFSTDTC', 'IT.DM.RFENDTC', 'IT.DM.RFXSTDTC', 'IT.DM.RFXENDTC', 'IT.DM.RFICDTC', 'IT.DM.RFPENDTC', 'IT.DM.DTHDTC', 'IT.DM.DTHFL', 'IT.DM.AGE', 'IT.DM.AGEU', 'IT.DM.SEX', 'IT.DM.RACE', 'IT.DM.ETHNIC', 'IT.DM.COUNTRY', 'IT.DM.ARM', 'IT.DM.ARMCD', 'IT.DM.ACTARM', 'IT.DM.ACTARMCD', 'IT.DM.DMDTC', 'IT.DM.DMDY'], 'keySequence': ['IT.DM.STUDYID', 'IT.DM.USUBJID']}, {'OID': 'IG.CM', 'name': 'CM', 'description': 'Concomitant Medications', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.CM.STUDYID', 'IT.CM.DOMAIN', 'IT.CM.USUBJID', 'IT.CM.CMSEQ', 'IT.CM.CMSPID', 'IT.CM.CMTRT', 'IT.CM.CMDECOD', 'IT.CM.CMINDC', 'IT.CM.CMCLAS', 'IT.CM.CMDOSE', 'IT.CM.CMDOSU', 'IT.CM.CMDOSFRQ', 'IT.CM.CMROUTE', 'IT.CM.VISITNUM', 'IT.CM.VISIT', 'IT.CM.VISITDY', 'IT.CM.CMDTC', 'IT.CM.CMSTDTC', 'IT.CM.CMENDTC', 'IT.CM.CMSTDY', 'IT.CM.CMENDY'], 'keySequence': ['IT.CM.STUDYID', 'IT.CM.USUBJID']}, {'OID': 'IG.SUPPDS', 'name': 'SUPPDS', 'description': 'Supplemental Qualifiers for DS', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.RDOMAIN', 'IT.SUPPDS.USUBJID', 'IT.SUPPDS.IDVAR', 'IT.SUPPDS.IDVARVAL', 'IT.SUPPDS.QNAM', 'IT.SUPPDS.QLABEL', 'IT.SUPPDS.QVAL', 'IT.SUPPDS.QORIG', 'IT.SUPPDS.QEVAL'], 'keySequence': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.USUBJID']}, {'OID': 'IG.EX', 'name': 'EX', 'description': 'Exposure', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.EX.STUDYID', 'IT.EX.DOMAIN', 'IT.EX.USUBJID', 'IT.EX.EXSEQ', 'IT.EX.EXTRT', 'IT.EX.EXDOSE', 'IT.EX.EXDOSU', 'IT.EX.EXDOSFRM', 'IT.EX.EXDOSFRQ', 'IT.EX.EXROUTE', 'IT.EX.VISITNUM', 'IT.EX.VISIT', 'IT.EX.VISITDY', 'IT.EX.EXSTDTC', 'IT.EX.EXENDTC', 'IT.EX.EXSTDY', 'IT.EX.EXENDY'], 'keySequence': ['IT.EX.STUDYID', 'IT.EX.USUBJID']}, {'OID': 'IG.VS', 'name': 'VS', 'description': 'Vital Signs', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.VS.STUDYID', 'IT.VS.DOMAIN', 'IT.VS.USUBJID', 'IT.VS.VSSEQ', 'IT.VS.VSTESTCD', 'IT.VS.VSTEST', 'IT.VS.VSPOS', 'IT.VS.VSORRES', 'IT.VS.VSORRESU', 'IT.VS.VSSTRESC', 'IT.VS.VSSTRESN', 'IT.VS.VSSTRESU', 'IT.VS.VSSTAT', 'IT.VS.VSLOC', 'IT.VS.VSBLFL', 'IT.VS.VISITNUM', 'IT.VS.VISIT', 'IT.VS.VISITDY', 'IT.VS.VSDTC', 'IT.VS.VSDY', 'IT.VS.VSTPT', 'IT.VS.VSTPTNUM', 'IT.VS.VSELTM', 'IT.VS.VSTPTREF'], 'keySequence': ['IT.VS.STUDYID', 'IT.VS.USUBJID']}, {'OID': 'IG.MH', 'name': 'MH', 'description': 'Medical History', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.MH.STUDYID', 'IT.MH.DOMAIN', 'IT.MH.USUBJID', 'IT.MH.MHSEQ', 'IT.MH.MHSPID', 'IT.MH.MHTERM', 'IT.MH.MHLLT', 'IT.MH.MHDECOD', 'IT.MH.MHHLT', 'IT.MH.MHHLGT', 'IT.MH.MHCAT', 'IT.MH.MHBODSYS', 'IT.MH.MHSEV', 'IT.MH.VISITNUM', 'IT.MH.VISIT', 'IT.MH.VISITDY', 'IT.MH.MHDTC', 'IT.MH.MHSTDTC', 'IT.MH.MHDY'], 'keySequence': ['IT.MH.STUDYID', 'IT.MH.USUBJID']}, {'OID': 'IG.DS', 'name': 'DS', 'description': 'Disposition', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DS.STUDYID', 'IT.DS.DOMAIN', 'IT.DS.USUBJID', 'IT.DS.DSSEQ', 'IT.DS.DSSPID', 'IT.DS.DSTERM', 'IT.DS.DSDECOD', 'IT.DS.DSCAT', 'IT.DS.VISITNUM', 'IT.DS.VISIT', 'IT.DS.DSDTC', 'IT.DS.DSSTDTC', 'IT.DS.DSSTDY'], 'keySequence': ['IT.DS.STUDYID', 'IT.DS.USUBJID']}], 'standards': [{'OID': 'STD.1', 'name': 'SDTMIG', 'type': 'IG', 'version': '3.4', 'status': 'Final'}, {'OID': 'STD.2', 'name': 'CDISC/NCI', 'type': 'CT', 'version': '2024-09-27', 'status': 'Final'}]} instance_index=0 instantiates='MetaDataVersion' context=["'IT.MH.STUDYID' is not of type 'object'", "'IT.MH.DOMAIN' is not of type 'object'", "'IT.MH.USUBJID' is not of type 'object'", "'IT.MH.MHSEQ' is not of type 'object'", "'IT.MH.MHSPID' is not of type 'object'", "'IT.MH.MHTERM' is not of type 'object'", "'IT.MH.MHLLT' is not of type 'object'", "'IT.MH.MHDECOD' is not of type 'object'", "'IT.MH.MHHLT' is not of type 'object'", "'IT.MH.MHHLGT' is not of type 'object'", "'IT.MH.MHCAT' is not of type 'object'", "'IT.MH.MHBODSYS' is not of type 'object'", "'IT.MH.MHSEV' is not of type 'object'", "'IT.MH.VISITNUM' is not of type 'object'", "'IT.MH.VISIT' is not of type 'object'", "'IT.MH.VISITDY' is not of type 'object'", "'IT.MH.MHDTC' is not of type 'object'", "'IT.MH.MHSTDTC' is not of type 'object'", "'IT.MH.MHDY' is not of type 'object'", "'IT.MH.STUDYID' is not of type 'object'", "'IT.MH.USUBJID' is not of type 'object'", "'IT.MH.STUDYID' is not of type 'object'", "'IT.MH.DOMAIN' is not of type 'object'", "'IT.MH.USUBJID' is not of type 'object'", "'IT.MH.MHSEQ' is not of type 'object'", "'IT.MH.MHSPID' is not of type 'object'", "'IT.MH.MHTERM' is not of type 'object'", "'IT.MH.MHLLT' is not of type 'object'", "'IT.MH.MHDECOD' is not of type 'object'", "'IT.MH.MHHLT' is not of type 'object'", "'IT.MH.MHHLGT' is not of type 'object'", "'IT.MH.MHCAT' is not of type 'object'", "'IT.MH.MHBODSYS' is not of type 'object'", "'IT.MH.MHSEV' is not of type 'object'", "'IT.MH.VISITNUM' is not of type 'object'", "'IT.MH.VISIT' is not of type 'object'", "'IT.MH.VISITDY' is not of type 'object'", "'IT.MH.MHDTC' is not of type 'object'", "'IT.MH.MHSTDTC' is not of type 'object'", "'IT.MH.MHDY' is not of type 'object'", "'IT.MH.STUDYID' is not of type 'object'", "'IT.MH.USUBJID' is not of type 'object'"] source=&lt;ValidationError: "{'OID': 'IG.MH', 'name': 'MH', 'description': 'Medical History', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.MH.STUDYID', 'IT.MH.DOMAIN', 'IT.MH.USUBJID', 'IT.MH.MHSEQ', 'IT.MH.MHSPID', 'IT.MH.MHTERM', 'IT.MH.MHLLT', 'IT.MH.MHDECOD', 'IT.MH.MHHLT', 'IT.MH.MHHLGT', 'IT.MH.MHCAT', 'IT.MH.MHBODSYS', 'IT.MH.MHSEV', 'IT.MH.VISITNUM', 'IT.MH.VISIT', 'IT.MH.VISITDY', 'IT.MH.MHDTC', 'IT.MH.MHSTDTC', 'IT.MH.MHDY'], 'keySequence': ['IT.MH.STUDYID', 'IT.MH.USUBJID']} is not valid under any of the given schemas"&gt;</t>
+          <t>'OID' is a required property in /items/180/origin/documents/0</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>type='jsonschema validation' severity=&lt;Severity.ERROR: 'ERROR'&gt; message="{'OID': 'IG.DS', 'name': 'DS', 'description': 'Disposition', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DS.STUDYID', 'IT.DS.DOMAIN', 'IT.DS.USUBJID', 'IT.DS.DSSEQ', 'IT.DS.DSSPID', 'IT.DS.DSTERM', 'IT.DS.DSDECOD', 'IT.DS.DSCAT', 'IT.DS.VISITNUM', 'IT.DS.VISIT', 'IT.DS.DSDTC', 'IT.DS.DSSTDTC', 'IT.DS.DSSTDY'], 'keySequence': ['IT.DS.STUDYID', 'IT.DS.USUBJID']} is not valid under any of the given schemas in /itemGroups/10" instance={'OID': 'MDV.360i CDISC PILOT - LZZT', 'name': 'MDV 360i CDISC PILOT - LZZT', 'description': 'Data Definitions for 360i CDISC PILOT - LZZT', 'fileOID': 'ODM.DEFINE-360I.360i CDISC PILOT - LZZT', 'creationDateTime': '2026-04-15T20:36:55.421402+00:00', 'odmVersion': '1.3.2', 'fileType': 'Snapshot', 'originator': 'Define-360i Processor', 'context': 'Other', 'defineVersion': '2.1.0', 'studyOID': '', 'studyName': '360i CDISC PILOT - LZZT', 'studyDescription': "Safety and Efficacy of the Xanomeline Transdermal Therapeutic System (TTS) in Patients with Mild to Moderate Alzheimer's Disease", 'protocolName': '360i LZZT Xanomeline (LY246708)', 'itemGroups': [{'OID': 'IG.SC', 'name': 'SC', 'description': 'Subject Characteristics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SC.STUDYID', 'IT.SC.DOMAIN', 'IT.SC.USUBJID', 'IT.SC.SCSEQ', 'IT.SC.SCTESTCD', 'IT.SC.SCTEST', 'IT.SC.SCCAT', 'IT.SC.SCORRES', 'IT.SC.SCORRESU', 'IT.SC.SCSTRESC', 'IT.SC.SCSTRESN', 'IT.SC.SCSTRESU', 'IT.SC.SCDTC', 'IT.SC.SCDY'], 'keySequence': ['IT.SC.STUDYID', 'IT.SC.USUBJID']}, {'OID': 'IG.LB', 'name': 'LB', 'description': 'Laboratory Test Findings', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.LB.STUDYID', 'IT.LB.DOMAIN', 'IT.LB.USUBJID', 'IT.LB.LBSEQ', 'IT.LB.LBTESTCD', 'IT.LB.LBTEST', 'IT.LB.LBCAT', 'IT.LB.LBORRES', 'IT.LB.LBORRESU', 'IT.LB.LBORNRLO', 'IT.LB.LBORNRHI', 'IT.LB.LBSTRESC', 'IT.LB.LBSTRESN', 'IT.LB.LBSTRESU', 'IT.LB.LBSTNRLO', 'IT.LB.LBSTNRHI', 'IT.LB.LBNRIND', 'IT.LB.LBBLFL', 'IT.LB.VISITNUM', 'IT.LB.VISIT', 'IT.LB.VISITDY', 'IT.LB.LBDTC', 'IT.LB.LBDY'], 'keySequence': ['IT.LB.STUDYID', 'IT.LB.USUBJID']}, {'OID': 'IG.AE', 'name': 'AE', 'description': 'Adverse Events', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.AE.STUDYID', 'IT.AE.DOMAIN', 'IT.AE.USUBJID', 'IT.AE.AESEQ', 'IT.AE.AESPID', 'IT.AE.AETERM', 'IT.AE.AELLT', 'IT.AE.AELLTCD', 'IT.AE.AEDECOD', 'IT.AE.AEPTCD', 'IT.AE.AEHLT', 'IT.AE.AEHLTCD', 'IT.AE.AEHLGT', 'IT.AE.AEHLGTCD', 'IT.AE.AEBODSYS', 'IT.AE.AEBDSYCD', 'IT.AE.AESOC', 'IT.AE.AESOCCD', 'IT.AE.AESEV', 'IT.AE.AESER', 'IT.AE.AEACN', 'IT.AE.AEREL', 'IT.AE.AEOUT', 'IT.AE.AESCAN', 'IT.AE.AESCONG', 'IT.AE.AESDISAB', 'IT.AE.AESDTH', 'IT.AE.AESHOSP', 'IT.AE.AESLIFE', 'IT.AE.AESOD', 'IT.AE.AEDTC', 'IT.AE.AESTDTC', 'IT.AE.AEENDTC', 'IT.AE.AESTDY', 'IT.AE.AEENDY'], 'keySequence': ['IT.AE.STUDYID', 'IT.AE.USUBJID']}, {'OID': 'IG.QS', 'name': 'QS', 'description': 'Questionnaires', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.QS.STUDYID', 'IT.QS.DOMAIN', 'IT.QS.USUBJID', 'IT.QS.QSSEQ', 'IT.QS.QSTESTCD', 'IT.QS.QSTEST', 'IT.QS.QSCAT', 'IT.QS.QSSCAT', 'IT.QS.QSORRES', 'IT.QS.QSORRESU', 'IT.QS.QSSTRESC', 'IT.QS.QSSTRESN', 'IT.QS.QSSTRESU', 'IT.QS.QSBLFL', 'IT.QS.QSDRVFL', 'IT.QS.VISITNUM', 'IT.QS.VISIT', 'IT.QS.VISITDY', 'IT.QS.QSDTC', 'IT.QS.QSDY'], 'keySequence': ['IT.QS.STUDYID', 'IT.QS.USUBJID']}, {'OID': 'IG.DM', 'name': 'DM', 'description': 'Demographics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DM.STUDYID', 'IT.DM.SITEID', 'IT.DM.DOMAIN', 'IT.DM.USUBJID', 'IT.DM.SUBJID', 'IT.DM.RFSTDTC', 'IT.DM.RFENDTC', 'IT.DM.RFXSTDTC', 'IT.DM.RFXENDTC', 'IT.DM.RFICDTC', 'IT.DM.RFPENDTC', 'IT.DM.DTHDTC', 'IT.DM.DTHFL', 'IT.DM.AGE', 'IT.DM.AGEU', 'IT.DM.SEX', 'IT.DM.RACE', 'IT.DM.ETHNIC', 'IT.DM.COUNTRY', 'IT.DM.ARM', 'IT.DM.ARMCD', 'IT.DM.ACTARM', 'IT.DM.ACTARMCD', 'IT.DM.DMDTC', 'IT.DM.DMDY'], 'keySequence': ['IT.DM.STUDYID', 'IT.DM.USUBJID']}, {'OID': 'IG.CM', 'name': 'CM', 'description': 'Concomitant Medications', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.CM.STUDYID', 'IT.CM.DOMAIN', 'IT.CM.USUBJID', 'IT.CM.CMSEQ', 'IT.CM.CMSPID', 'IT.CM.CMTRT', 'IT.CM.CMDECOD', 'IT.CM.CMINDC', 'IT.CM.CMCLAS', 'IT.CM.CMDOSE', 'IT.CM.CMDOSU', 'IT.CM.CMDOSFRQ', 'IT.CM.CMROUTE', 'IT.CM.VISITNUM', 'IT.CM.VISIT', 'IT.CM.VISITDY', 'IT.CM.CMDTC', 'IT.CM.CMSTDTC', 'IT.CM.CMENDTC', 'IT.CM.CMSTDY', 'IT.CM.CMENDY'], 'keySequence': ['IT.CM.STUDYID', 'IT.CM.USUBJID']}, {'OID': 'IG.SUPPDS', 'name': 'SUPPDS', 'description': 'Supplemental Qualifiers for DS', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.RDOMAIN', 'IT.SUPPDS.USUBJID', 'IT.SUPPDS.IDVAR', 'IT.SUPPDS.IDVARVAL', 'IT.SUPPDS.QNAM', 'IT.SUPPDS.QLABEL', 'IT.SUPPDS.QVAL', 'IT.SUPPDS.QORIG', 'IT.SUPPDS.QEVAL'], 'keySequence': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.USUBJID']}, {'OID': 'IG.EX', 'name': 'EX', 'description': 'Exposure', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.EX.STUDYID', 'IT.EX.DOMAIN', 'IT.EX.USUBJID', 'IT.EX.EXSEQ', 'IT.EX.EXTRT', 'IT.EX.EXDOSE', 'IT.EX.EXDOSU', 'IT.EX.EXDOSFRM', 'IT.EX.EXDOSFRQ', 'IT.EX.EXROUTE', 'IT.EX.VISITNUM', 'IT.EX.VISIT', 'IT.EX.VISITDY', 'IT.EX.EXSTDTC', 'IT.EX.EXENDTC', 'IT.EX.EXSTDY', 'IT.EX.EXENDY'], 'keySequence': ['IT.EX.STUDYID', 'IT.EX.USUBJID']}, {'OID': 'IG.VS', 'name': 'VS', 'description': 'Vital Signs', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.VS.STUDYID', 'IT.VS.DOMAIN', 'IT.VS.USUBJID', 'IT.VS.VSSEQ', 'IT.VS.VSTESTCD', 'IT.VS.VSTEST', 'IT.VS.VSPOS', 'IT.VS.VSORRES', 'IT.VS.VSORRESU', 'IT.VS.VSSTRESC', 'IT.VS.VSSTRESN', 'IT.VS.VSSTRESU', 'IT.VS.VSSTAT', 'IT.VS.VSLOC', 'IT.VS.VSBLFL', 'IT.VS.VISITNUM', 'IT.VS.VISIT', 'IT.VS.VISITDY', 'IT.VS.VSDTC', 'IT.VS.VSDY', 'IT.VS.VSTPT', 'IT.VS.VSTPTNUM', 'IT.VS.VSELTM', 'IT.VS.VSTPTREF'], 'keySequence': ['IT.VS.STUDYID', 'IT.VS.USUBJID']}, {'OID': 'IG.MH', 'name': 'MH', 'description': 'Medical History', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.MH.STUDYID', 'IT.MH.DOMAIN', 'IT.MH.USUBJID', 'IT.MH.MHSEQ', 'IT.MH.MHSPID', 'IT.MH.MHTERM', 'IT.MH.MHLLT', 'IT.MH.MHDECOD', 'IT.MH.MHHLT', 'IT.MH.MHHLGT', 'IT.MH.MHCAT', 'IT.MH.MHBODSYS', 'IT.MH.MHSEV', 'IT.MH.VISITNUM', 'IT.MH.VISIT', 'IT.MH.VISITDY', 'IT.MH.MHDTC', 'IT.MH.MHSTDTC', 'IT.MH.MHDY'], 'keySequence': ['IT.MH.STUDYID', 'IT.MH.USUBJID']}, {'OID': 'IG.DS', 'name': 'DS', 'description': 'Disposition', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DS.STUDYID', 'IT.DS.DOMAIN', 'IT.DS.USUBJID', 'IT.DS.DSSEQ', 'IT.DS.DSSPID', 'IT.DS.DSTERM', 'IT.DS.DSDECOD', 'IT.DS.DSCAT', 'IT.DS.VISITNUM', 'IT.DS.VISIT', 'IT.DS.DSDTC', 'IT.DS.DSSTDTC', 'IT.DS.DSSTDY'], 'keySequence': ['IT.DS.STUDYID', 'IT.DS.USUBJID']}], 'standards': [{'OID': 'STD.1', 'name': 'SDTMIG', 'type': 'IG', 'version': '3.4', 'status': 'Final'}, {'OID': 'STD.2', 'name': 'CDISC/NCI', 'type': 'CT', 'version': '2024-09-27', 'status': 'Final'}]} instance_index=0 instantiates='MetaDataVersion' context=["'IT.DS.STUDYID' is not of type 'object'", "'IT.DS.DOMAIN' is not of type 'object'", "'IT.DS.USUBJID' is not of type 'object'", "'IT.DS.DSSEQ' is not of type 'object'", "'IT.DS.DSSPID' is not of type 'object'", "'IT.DS.DSTERM' is not of type 'object'", "'IT.DS.DSDECOD' is not of type 'object'", "'IT.DS.DSCAT' is not of type 'object'", "'IT.DS.VISITNUM' is not of type 'object'", "'IT.DS.VISIT' is not of type 'object'", "'IT.DS.DSDTC' is not of type 'object'", "'IT.DS.DSSTDTC' is not of type 'object'", "'IT.DS.DSSTDY' is not of type 'object'", "'IT.DS.STUDYID' is not of type 'object'", "'IT.DS.USUBJID' is not of type 'object'", "'IT.DS.STUDYID' is not of type 'object'", "'IT.DS.DOMAIN' is not of type 'object'", "'IT.DS.USUBJID' is not of type 'object'", "'IT.DS.DSSEQ' is not of type 'object'", "'IT.DS.DSSPID' is not of type 'object'", "'IT.DS.DSTERM' is not of type 'object'", "'IT.DS.DSDECOD' is not of type 'object'", "'IT.DS.DSCAT' is not of type 'object'", "'IT.DS.VISITNUM' is not of type 'object'", "'IT.DS.VISIT' is not of type 'object'", "'IT.DS.DSDTC' is not of type 'object'", "'IT.DS.DSSTDTC' is not of type 'object'", "'IT.DS.DSSTDY' is not of type 'object'", "'IT.DS.STUDYID' is not of type 'object'", "'IT.DS.USUBJID' is not of type 'object'"] source=&lt;ValidationError: "{'OID': 'IG.DS', 'name': 'DS', 'description': 'Disposition', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DS.STUDYID', 'IT.DS.DOMAIN', 'IT.DS.USUBJID', 'IT.DS.DSSEQ', 'IT.DS.DSSPID', 'IT.DS.DSTERM', 'IT.DS.DSDECOD', 'IT.DS.DSCAT', 'IT.DS.VISITNUM', 'IT.DS.VISIT', 'IT.DS.DSDTC', 'IT.DS.DSSTDTC', 'IT.DS.DSSTDY'], 'keySequence': ['IT.DS.STUDYID', 'IT.DS.USUBJID']} is not valid under any of the given schemas"&gt;</t>
+          <t>'OID' is a required property in /items/181/origin/documents/0</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>type='jsonschema validation' severity=&lt;Severity.ERROR: 'ERROR'&gt; message="'Final' is not one of ['DRAFT', 'FINAL'] in /standards/0/status" instance={'OID': 'MDV.360i CDISC PILOT - LZZT', 'name': 'MDV 360i CDISC PILOT - LZZT', 'description': 'Data Definitions for 360i CDISC PILOT - LZZT', 'fileOID': 'ODM.DEFINE-360I.360i CDISC PILOT - LZZT', 'creationDateTime': '2026-04-15T20:36:55.421402+00:00', 'odmVersion': '1.3.2', 'fileType': 'Snapshot', 'originator': 'Define-360i Processor', 'context': 'Other', 'defineVersion': '2.1.0', 'studyOID': '', 'studyName': '360i CDISC PILOT - LZZT', 'studyDescription': "Safety and Efficacy of the Xanomeline Transdermal Therapeutic System (TTS) in Patients with Mild to Moderate Alzheimer's Disease", 'protocolName': '360i LZZT Xanomeline (LY246708)', 'itemGroups': [{'OID': 'IG.SC', 'name': 'SC', 'description': 'Subject Characteristics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SC.STUDYID', 'IT.SC.DOMAIN', 'IT.SC.USUBJID', 'IT.SC.SCSEQ', 'IT.SC.SCTESTCD', 'IT.SC.SCTEST', 'IT.SC.SCCAT', 'IT.SC.SCORRES', 'IT.SC.SCORRESU', 'IT.SC.SCSTRESC', 'IT.SC.SCSTRESN', 'IT.SC.SCSTRESU', 'IT.SC.SCDTC', 'IT.SC.SCDY'], 'keySequence': ['IT.SC.STUDYID', 'IT.SC.USUBJID']}, {'OID': 'IG.LB', 'name': 'LB', 'description': 'Laboratory Test Findings', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.LB.STUDYID', 'IT.LB.DOMAIN', 'IT.LB.USUBJID', 'IT.LB.LBSEQ', 'IT.LB.LBTESTCD', 'IT.LB.LBTEST', 'IT.LB.LBCAT', 'IT.LB.LBORRES', 'IT.LB.LBORRESU', 'IT.LB.LBORNRLO', 'IT.LB.LBORNRHI', 'IT.LB.LBSTRESC', 'IT.LB.LBSTRESN', 'IT.LB.LBSTRESU', 'IT.LB.LBSTNRLO', 'IT.LB.LBSTNRHI', 'IT.LB.LBNRIND', 'IT.LB.LBBLFL', 'IT.LB.VISITNUM', 'IT.LB.VISIT', 'IT.LB.VISITDY', 'IT.LB.LBDTC', 'IT.LB.LBDY'], 'keySequence': ['IT.LB.STUDYID', 'IT.LB.USUBJID']}, {'OID': 'IG.AE', 'name': 'AE', 'description': 'Adverse Events', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.AE.STUDYID', 'IT.AE.DOMAIN', 'IT.AE.USUBJID', 'IT.AE.AESEQ', 'IT.AE.AESPID', 'IT.AE.AETERM', 'IT.AE.AELLT', 'IT.AE.AELLTCD', 'IT.AE.AEDECOD', 'IT.AE.AEPTCD', 'IT.AE.AEHLT', 'IT.AE.AEHLTCD', 'IT.AE.AEHLGT', 'IT.AE.AEHLGTCD', 'IT.AE.AEBODSYS', 'IT.AE.AEBDSYCD', 'IT.AE.AESOC', 'IT.AE.AESOCCD', 'IT.AE.AESEV', 'IT.AE.AESER', 'IT.AE.AEACN', 'IT.AE.AEREL', 'IT.AE.AEOUT', 'IT.AE.AESCAN', 'IT.AE.AESCONG', 'IT.AE.AESDISAB', 'IT.AE.AESDTH', 'IT.AE.AESHOSP', 'IT.AE.AESLIFE', 'IT.AE.AESOD', 'IT.AE.AEDTC', 'IT.AE.AESTDTC', 'IT.AE.AEENDTC', 'IT.AE.AESTDY', 'IT.AE.AEENDY'], 'keySequence': ['IT.AE.STUDYID', 'IT.AE.USUBJID']}, {'OID': 'IG.QS', 'name': 'QS', 'description': 'Questionnaires', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.QS.STUDYID', 'IT.QS.DOMAIN', 'IT.QS.USUBJID', 'IT.QS.QSSEQ', 'IT.QS.QSTESTCD', 'IT.QS.QSTEST', 'IT.QS.QSCAT', 'IT.QS.QSSCAT', 'IT.QS.QSORRES', 'IT.QS.QSORRESU', 'IT.QS.QSSTRESC', 'IT.QS.QSSTRESN', 'IT.QS.QSSTRESU', 'IT.QS.QSBLFL', 'IT.QS.QSDRVFL', 'IT.QS.VISITNUM', 'IT.QS.VISIT', 'IT.QS.VISITDY', 'IT.QS.QSDTC', 'IT.QS.QSDY'], 'keySequence': ['IT.QS.STUDYID', 'IT.QS.USUBJID']}, {'OID': 'IG.DM', 'name': 'DM', 'description': 'Demographics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DM.STUDYID', 'IT.DM.SITEID', 'IT.DM.DOMAIN', 'IT.DM.USUBJID', 'IT.DM.SUBJID', 'IT.DM.RFSTDTC', 'IT.DM.RFENDTC', 'IT.DM.RFXSTDTC', 'IT.DM.RFXENDTC', 'IT.DM.RFICDTC', 'IT.DM.RFPENDTC', 'IT.DM.DTHDTC', 'IT.DM.DTHFL', 'IT.DM.AGE', 'IT.DM.AGEU', 'IT.DM.SEX', 'IT.DM.RACE', 'IT.DM.ETHNIC', 'IT.DM.COUNTRY', 'IT.DM.ARM', 'IT.DM.ARMCD', 'IT.DM.ACTARM', 'IT.DM.ACTARMCD', 'IT.DM.DMDTC', 'IT.DM.DMDY'], 'keySequence': ['IT.DM.STUDYID', 'IT.DM.USUBJID']}, {'OID': 'IG.CM', 'name': 'CM', 'description': 'Concomitant Medications', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.CM.STUDYID', 'IT.CM.DOMAIN', 'IT.CM.USUBJID', 'IT.CM.CMSEQ', 'IT.CM.CMSPID', 'IT.CM.CMTRT', 'IT.CM.CMDECOD', 'IT.CM.CMINDC', 'IT.CM.CMCLAS', 'IT.CM.CMDOSE', 'IT.CM.CMDOSU', 'IT.CM.CMDOSFRQ', 'IT.CM.CMROUTE', 'IT.CM.VISITNUM', 'IT.CM.VISIT', 'IT.CM.VISITDY', 'IT.CM.CMDTC', 'IT.CM.CMSTDTC', 'IT.CM.CMENDTC', 'IT.CM.CMSTDY', 'IT.CM.CMENDY'], 'keySequence': ['IT.CM.STUDYID', 'IT.CM.USUBJID']}, {'OID': 'IG.SUPPDS', 'name': 'SUPPDS', 'description': 'Supplemental Qualifiers for DS', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.RDOMAIN', 'IT.SUPPDS.USUBJID', 'IT.SUPPDS.IDVAR', 'IT.SUPPDS.IDVARVAL', 'IT.SUPPDS.QNAM', 'IT.SUPPDS.QLABEL', 'IT.SUPPDS.QVAL', 'IT.SUPPDS.QORIG', 'IT.SUPPDS.QEVAL'], 'keySequence': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.USUBJID']}, {'OID': 'IG.EX', 'name': 'EX', 'description': 'Exposure', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.EX.STUDYID', 'IT.EX.DOMAIN', 'IT.EX.USUBJID', 'IT.EX.EXSEQ', 'IT.EX.EXTRT', 'IT.EX.EXDOSE', 'IT.EX.EXDOSU', 'IT.EX.EXDOSFRM', 'IT.EX.EXDOSFRQ', 'IT.EX.EXROUTE', 'IT.EX.VISITNUM', 'IT.EX.VISIT', 'IT.EX.VISITDY', 'IT.EX.EXSTDTC', 'IT.EX.EXENDTC', 'IT.EX.EXSTDY', 'IT.EX.EXENDY'], 'keySequence': ['IT.EX.STUDYID', 'IT.EX.USUBJID']}, {'OID': 'IG.VS', 'name': 'VS', 'description': 'Vital Signs', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.VS.STUDYID', 'IT.VS.DOMAIN', 'IT.VS.USUBJID', 'IT.VS.VSSEQ', 'IT.VS.VSTESTCD', 'IT.VS.VSTEST', 'IT.VS.VSPOS', 'IT.VS.VSORRES', 'IT.VS.VSORRESU', 'IT.VS.VSSTRESC', 'IT.VS.VSSTRESN', 'IT.VS.VSSTRESU', 'IT.VS.VSSTAT', 'IT.VS.VSLOC', 'IT.VS.VSBLFL', 'IT.VS.VISITNUM', 'IT.VS.VISIT', 'IT.VS.VISITDY', 'IT.VS.VSDTC', 'IT.VS.VSDY', 'IT.VS.VSTPT', 'IT.VS.VSTPTNUM', 'IT.VS.VSELTM', 'IT.VS.VSTPTREF'], 'keySequence': ['IT.VS.STUDYID', 'IT.VS.USUBJID']}, {'OID': 'IG.MH', 'name': 'MH', 'description': 'Medical History', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.MH.STUDYID', 'IT.MH.DOMAIN', 'IT.MH.USUBJID', 'IT.MH.MHSEQ', 'IT.MH.MHSPID', 'IT.MH.MHTERM', 'IT.MH.MHLLT', 'IT.MH.MHDECOD', 'IT.MH.MHHLT', 'IT.MH.MHHLGT', 'IT.MH.MHCAT', 'IT.MH.MHBODSYS', 'IT.MH.MHSEV', 'IT.MH.VISITNUM', 'IT.MH.VISIT', 'IT.MH.VISITDY', 'IT.MH.MHDTC', 'IT.MH.MHSTDTC', 'IT.MH.MHDY'], 'keySequence': ['IT.MH.STUDYID', 'IT.MH.USUBJID']}, {'OID': 'IG.DS', 'name': 'DS', 'description': 'Disposition', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DS.STUDYID', 'IT.DS.DOMAIN', 'IT.DS.USUBJID', 'IT.DS.DSSEQ', 'IT.DS.DSSPID', 'IT.DS.DSTERM', 'IT.DS.DSDECOD', 'IT.DS.DSCAT', 'IT.DS.VISITNUM', 'IT.DS.VISIT', 'IT.DS.DSDTC', 'IT.DS.DSSTDTC', 'IT.DS.DSSTDY'], 'keySequence': ['IT.DS.STUDYID', 'IT.DS.USUBJID']}], 'standards': [{'OID': 'STD.1', 'name': 'SDTMIG', 'type': 'IG', 'version': '3.4', 'status': 'Final'}, {'OID': 'STD.2', 'name': 'CDISC/NCI', 'type': 'CT', 'version': '2024-09-27', 'status': 'Final'}]} instance_index=0 instantiates='MetaDataVersion' context=[] source=&lt;ValidationError: "'Final' is not one of ['DRAFT', 'FINAL']"&gt;</t>
+          <t>'OID' is a required property in /items/182/origin/documents/0</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,137 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>type='jsonschema validation' severity=&lt;Severity.ERROR: 'ERROR'&gt; message="'Final' is not one of ['DRAFT', 'FINAL'] in /standards/1/status" instance={'OID': 'MDV.360i CDISC PILOT - LZZT', 'name': 'MDV 360i CDISC PILOT - LZZT', 'description': 'Data Definitions for 360i CDISC PILOT - LZZT', 'fileOID': 'ODM.DEFINE-360I.360i CDISC PILOT - LZZT', 'creationDateTime': '2026-04-15T20:36:55.421402+00:00', 'odmVersion': '1.3.2', 'fileType': 'Snapshot', 'originator': 'Define-360i Processor', 'context': 'Other', 'defineVersion': '2.1.0', 'studyOID': '', 'studyName': '360i CDISC PILOT - LZZT', 'studyDescription': "Safety and Efficacy of the Xanomeline Transdermal Therapeutic System (TTS) in Patients with Mild to Moderate Alzheimer's Disease", 'protocolName': '360i LZZT Xanomeline (LY246708)', 'itemGroups': [{'OID': 'IG.SC', 'name': 'SC', 'description': 'Subject Characteristics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SC.STUDYID', 'IT.SC.DOMAIN', 'IT.SC.USUBJID', 'IT.SC.SCSEQ', 'IT.SC.SCTESTCD', 'IT.SC.SCTEST', 'IT.SC.SCCAT', 'IT.SC.SCORRES', 'IT.SC.SCORRESU', 'IT.SC.SCSTRESC', 'IT.SC.SCSTRESN', 'IT.SC.SCSTRESU', 'IT.SC.SCDTC', 'IT.SC.SCDY'], 'keySequence': ['IT.SC.STUDYID', 'IT.SC.USUBJID']}, {'OID': 'IG.LB', 'name': 'LB', 'description': 'Laboratory Test Findings', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.LB.STUDYID', 'IT.LB.DOMAIN', 'IT.LB.USUBJID', 'IT.LB.LBSEQ', 'IT.LB.LBTESTCD', 'IT.LB.LBTEST', 'IT.LB.LBCAT', 'IT.LB.LBORRES', 'IT.LB.LBORRESU', 'IT.LB.LBORNRLO', 'IT.LB.LBORNRHI', 'IT.LB.LBSTRESC', 'IT.LB.LBSTRESN', 'IT.LB.LBSTRESU', 'IT.LB.LBSTNRLO', 'IT.LB.LBSTNRHI', 'IT.LB.LBNRIND', 'IT.LB.LBBLFL', 'IT.LB.VISITNUM', 'IT.LB.VISIT', 'IT.LB.VISITDY', 'IT.LB.LBDTC', 'IT.LB.LBDY'], 'keySequence': ['IT.LB.STUDYID', 'IT.LB.USUBJID']}, {'OID': 'IG.AE', 'name': 'AE', 'description': 'Adverse Events', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.AE.STUDYID', 'IT.AE.DOMAIN', 'IT.AE.USUBJID', 'IT.AE.AESEQ', 'IT.AE.AESPID', 'IT.AE.AETERM', 'IT.AE.AELLT', 'IT.AE.AELLTCD', 'IT.AE.AEDECOD', 'IT.AE.AEPTCD', 'IT.AE.AEHLT', 'IT.AE.AEHLTCD', 'IT.AE.AEHLGT', 'IT.AE.AEHLGTCD', 'IT.AE.AEBODSYS', 'IT.AE.AEBDSYCD', 'IT.AE.AESOC', 'IT.AE.AESOCCD', 'IT.AE.AESEV', 'IT.AE.AESER', 'IT.AE.AEACN', 'IT.AE.AEREL', 'IT.AE.AEOUT', 'IT.AE.AESCAN', 'IT.AE.AESCONG', 'IT.AE.AESDISAB', 'IT.AE.AESDTH', 'IT.AE.AESHOSP', 'IT.AE.AESLIFE', 'IT.AE.AESOD', 'IT.AE.AEDTC', 'IT.AE.AESTDTC', 'IT.AE.AEENDTC', 'IT.AE.AESTDY', 'IT.AE.AEENDY'], 'keySequence': ['IT.AE.STUDYID', 'IT.AE.USUBJID']}, {'OID': 'IG.QS', 'name': 'QS', 'description': 'Questionnaires', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.QS.STUDYID', 'IT.QS.DOMAIN', 'IT.QS.USUBJID', 'IT.QS.QSSEQ', 'IT.QS.QSTESTCD', 'IT.QS.QSTEST', 'IT.QS.QSCAT', 'IT.QS.QSSCAT', 'IT.QS.QSORRES', 'IT.QS.QSORRESU', 'IT.QS.QSSTRESC', 'IT.QS.QSSTRESN', 'IT.QS.QSSTRESU', 'IT.QS.QSBLFL', 'IT.QS.QSDRVFL', 'IT.QS.VISITNUM', 'IT.QS.VISIT', 'IT.QS.VISITDY', 'IT.QS.QSDTC', 'IT.QS.QSDY'], 'keySequence': ['IT.QS.STUDYID', 'IT.QS.USUBJID']}, {'OID': 'IG.DM', 'name': 'DM', 'description': 'Demographics', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DM.STUDYID', 'IT.DM.SITEID', 'IT.DM.DOMAIN', 'IT.DM.USUBJID', 'IT.DM.SUBJID', 'IT.DM.RFSTDTC', 'IT.DM.RFENDTC', 'IT.DM.RFXSTDTC', 'IT.DM.RFXENDTC', 'IT.DM.RFICDTC', 'IT.DM.RFPENDTC', 'IT.DM.DTHDTC', 'IT.DM.DTHFL', 'IT.DM.AGE', 'IT.DM.AGEU', 'IT.DM.SEX', 'IT.DM.RACE', 'IT.DM.ETHNIC', 'IT.DM.COUNTRY', 'IT.DM.ARM', 'IT.DM.ARMCD', 'IT.DM.ACTARM', 'IT.DM.ACTARMCD', 'IT.DM.DMDTC', 'IT.DM.DMDY'], 'keySequence': ['IT.DM.STUDYID', 'IT.DM.USUBJID']}, {'OID': 'IG.CM', 'name': 'CM', 'description': 'Concomitant Medications', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.CM.STUDYID', 'IT.CM.DOMAIN', 'IT.CM.USUBJID', 'IT.CM.CMSEQ', 'IT.CM.CMSPID', 'IT.CM.CMTRT', 'IT.CM.CMDECOD', 'IT.CM.CMINDC', 'IT.CM.CMCLAS', 'IT.CM.CMDOSE', 'IT.CM.CMDOSU', 'IT.CM.CMDOSFRQ', 'IT.CM.CMROUTE', 'IT.CM.VISITNUM', 'IT.CM.VISIT', 'IT.CM.VISITDY', 'IT.CM.CMDTC', 'IT.CM.CMSTDTC', 'IT.CM.CMENDTC', 'IT.CM.CMSTDY', 'IT.CM.CMENDY'], 'keySequence': ['IT.CM.STUDYID', 'IT.CM.USUBJID']}, {'OID': 'IG.SUPPDS', 'name': 'SUPPDS', 'description': 'Supplemental Qualifiers for DS', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.RDOMAIN', 'IT.SUPPDS.USUBJID', 'IT.SUPPDS.IDVAR', 'IT.SUPPDS.IDVARVAL', 'IT.SUPPDS.QNAM', 'IT.SUPPDS.QLABEL', 'IT.SUPPDS.QVAL', 'IT.SUPPDS.QORIG', 'IT.SUPPDS.QEVAL'], 'keySequence': ['IT.SUPPDS.STUDYID', 'IT.SUPPDS.USUBJID']}, {'OID': 'IG.EX', 'name': 'EX', 'description': 'Exposure', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.EX.STUDYID', 'IT.EX.DOMAIN', 'IT.EX.USUBJID', 'IT.EX.EXSEQ', 'IT.EX.EXTRT', 'IT.EX.EXDOSE', 'IT.EX.EXDOSU', 'IT.EX.EXDOSFRM', 'IT.EX.EXDOSFRQ', 'IT.EX.EXROUTE', 'IT.EX.VISITNUM', 'IT.EX.VISIT', 'IT.EX.VISITDY', 'IT.EX.EXSTDTC', 'IT.EX.EXENDTC', 'IT.EX.EXSTDY', 'IT.EX.EXENDY'], 'keySequence': ['IT.EX.STUDYID', 'IT.EX.USUBJID']}, {'OID': 'IG.VS', 'name': 'VS', 'description': 'Vital Signs', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.VS.STUDYID', 'IT.VS.DOMAIN', 'IT.VS.USUBJID', 'IT.VS.VSSEQ', 'IT.VS.VSTESTCD', 'IT.VS.VSTEST', 'IT.VS.VSPOS', 'IT.VS.VSORRES', 'IT.VS.VSORRESU', 'IT.VS.VSSTRESC', 'IT.VS.VSSTRESN', 'IT.VS.VSSTRESU', 'IT.VS.VSSTAT', 'IT.VS.VSLOC', 'IT.VS.VSBLFL', 'IT.VS.VISITNUM', 'IT.VS.VISIT', 'IT.VS.VISITDY', 'IT.VS.VSDTC', 'IT.VS.VSDY', 'IT.VS.VSTPT', 'IT.VS.VSTPTNUM', 'IT.VS.VSELTM', 'IT.VS.VSTPTREF'], 'keySequence': ['IT.VS.STUDYID', 'IT.VS.USUBJID']}, {'OID': 'IG.MH', 'name': 'MH', 'description': 'Medical History', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.MH.STUDYID', 'IT.MH.DOMAIN', 'IT.MH.USUBJID', 'IT.MH.MHSEQ', 'IT.MH.MHSPID', 'IT.MH.MHTERM', 'IT.MH.MHLLT', 'IT.MH.MHDECOD', 'IT.MH.MHHLT', 'IT.MH.MHHLGT', 'IT.MH.MHCAT', 'IT.MH.MHBODSYS', 'IT.MH.MHSEV', 'IT.MH.VISITNUM', 'IT.MH.VISIT', 'IT.MH.VISITDY', 'IT.MH.MHDTC', 'IT.MH.MHSTDTC', 'IT.MH.MHDY'], 'keySequence': ['IT.MH.STUDYID', 'IT.MH.USUBJID']}, {'OID': 'IG.DS', 'name': 'DS', 'description': 'Disposition', 'structure': 'One record per vital sign measurement per visit per subject', 'purpose': 'Tabulation', 'standard': 'STD.1', 'items': ['IT.DS.STUDYID', 'IT.DS.DOMAIN', 'IT.DS.USUBJID', 'IT.DS.DSSEQ', 'IT.DS.DSSPID', 'IT.DS.DSTERM', 'IT.DS.DSDECOD', 'IT.DS.DSCAT', 'IT.DS.VISITNUM', 'IT.DS.VISIT', 'IT.DS.DSDTC', 'IT.DS.DSSTDTC', 'IT.DS.DSSTDY'], 'keySequence': ['IT.DS.STUDYID', 'IT.DS.USUBJID']}], 'standards': [{'OID': 'STD.1', 'name': 'SDTMIG', 'type': 'IG', 'version': '3.4', 'status': 'Final'}, {'OID': 'STD.2', 'name': 'CDISC/NCI', 'type': 'CT', 'version': '2024-09-27', 'status': 'Final'}]} instance_index=0 instantiates='MetaDataVersion' context=[] source=&lt;ValidationError: "'Final' is not one of ['DRAFT', 'FINAL']"&gt;</t>
+          <t>'OID' is a required property in /items/183/origin/documents/0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>'OID' is a required property in /items/203/origin/documents/0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>'OID' is a required property in /items/208/origin/documents/0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>{'OID': 'MT.LB.LBNRIND', 'name': 'LBNRIND Name', 'type': 'Computation', 'description': 'Derivation for LB.LBNRIND', 'documents': {'leafID': 'LF.COMPALGS', 'pages': [59, 60, 68]}} is not valid under any of the given schemas in /methods/0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>{'OID': 'MT.VS.HR', 'name': 'HR Name', 'type': 'Computation', 'description': 'Derivation for VS.HR', 'expressions': [{'expression': 'HR Expression Code', 'context': 'HR Expression Code'}]} is not valid under any of the given schemas in /methods/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>57 is not of type 'string', 'null' in /dictionaries/0/version</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>'Final' is not one of ['DRAFT', 'FINAL'] in /standards/0/status</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>'Final' is not one of ['DRAFT', 'FINAL'] in /standards/1/status</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>{'OID': 'LF.ACRF', 'leafID': 'LF.ACRF', 'title': 'Annotated CRF', 'href': 'acrf.pdf'} is not valid under any of the given schemas in /resources/0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>{'OID': 'LF.ACRF2', 'leafID': 'LF.ACRF2', 'title': 'Annotated CRF 2', 'href': 'acrf2.pdf'} is not valid under any of the given schemas in /resources/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>{'OID': 'LF.COMPALGS', 'leafID': 'LF.COMPALGS', 'title': 'Computational Algorithms', 'href': 'compalgs.pdf'} is not valid under any of the given schemas in /resources/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>{'OID': 'COM.STD1', 'text': 'This is a comment for SDTM standard'} is not of type 'string' in /comments/0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>{'OID': 'COM.QS', 'text': 'QS Comment'} is not of type 'string' in /comments/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>{'OID': 'COM.SYSBP', 'text': 'SYSBP Comment', 'documents': {'leafID': 'LF.COMPALGS', 'pages': ['10.0']}} is not of type 'string' in /comments/2</t>
         </is>
       </c>
     </row>
